--- a/public/docs/Plantilla Cursos Extensión - CIDIAM.xlsx
+++ b/public/docs/Plantilla Cursos Extensión - CIDIAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{295F07E8-2423-44A1-8A43-C99DF1BADF55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E039E749-1C82-48D2-881E-967EF8ED430A}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{295F07E8-2423-44A1-8A43-C99DF1BADF55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41014500-6919-4621-9F98-823CFE9FC5ED}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="243">
   <si>
     <t>Obligatorio</t>
   </si>
@@ -690,10 +690,6 @@
   </si>
   <si>
     <t>Opcional
-Fecha Fin</t>
-  </si>
-  <si>
-    <t>Opcional
 Fecha Inicio</t>
   </si>
   <si>
@@ -718,9 +714,6 @@
   </si>
   <si>
     <t>docformato</t>
-  </si>
-  <si>
-    <t>fechafin</t>
   </si>
   <si>
     <t>fechainicio</t>
@@ -2116,105 +2109,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>(Ejemplo: 05 de mayo de 2025)</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO" sz="1100" b="0">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-            <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="CuadroTexto 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC111E91-FC70-2E1E-D591-1A369C47F238}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16436340" y="731520"/>
-          <a:ext cx="2026920" cy="434340"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-CO" sz="1100" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>FECHA FIN CURSO</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="es-CO" sz="1100" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="es-CO" sz="1100" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>(Ejemplo: 06 de mayo de 2025)</a:t>
+            <a:t>(Ejemplo: 5 al 7 de mayo de 2025)</a:t>
           </a:r>
           <a:endParaRPr lang="es-CO" sz="1100" b="0">
             <a:solidFill>
@@ -2327,13 +2222,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2425,13 +2320,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2523,13 +2418,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2621,13 +2516,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
@@ -2703,13 +2598,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -2785,13 +2680,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -2867,13 +2762,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>792480</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -3139,13 +3034,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -3222,7 +3117,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>(Ejemplo: 06 de mayo de 2025)</a:t>
+            <a:t>(Ejemplo: 6 de mayo de 2025)</a:t>
           </a:r>
           <a:endParaRPr lang="es-CO" sz="1100" b="0">
             <a:solidFill>
@@ -3634,7 +3529,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:AA313"/>
+  <dimension ref="A1:Z313"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.8984375" style="8" customWidth="1"/>
@@ -3652,17 +3547,17 @@
     <col min="16" max="16" width="21.59765625" style="6" customWidth="1"/>
     <col min="17" max="17" width="29.3984375" style="6" customWidth="1"/>
     <col min="18" max="18" width="19.8984375" style="32" customWidth="1"/>
-    <col min="19" max="21" width="27.69921875" style="6" customWidth="1"/>
-    <col min="22" max="22" width="31.3984375" style="6" customWidth="1"/>
-    <col min="23" max="23" width="34" style="6" customWidth="1"/>
-    <col min="24" max="24" width="31.3984375" style="6" customWidth="1"/>
-    <col min="25" max="25" width="9.69921875" style="26" customWidth="1"/>
-    <col min="26" max="26" width="9.69921875" style="29" customWidth="1"/>
-    <col min="27" max="27" width="9.69921875" style="15" customWidth="1"/>
-    <col min="28" max="16384" width="10.5" style="3"/>
+    <col min="19" max="20" width="27.69921875" style="6" customWidth="1"/>
+    <col min="21" max="21" width="31.3984375" style="6" customWidth="1"/>
+    <col min="22" max="22" width="34" style="6" customWidth="1"/>
+    <col min="23" max="23" width="31.3984375" style="6" customWidth="1"/>
+    <col min="24" max="24" width="9.69921875" style="26" customWidth="1"/>
+    <col min="25" max="25" width="9.69921875" style="29" customWidth="1"/>
+    <col min="26" max="26" width="9.69921875" style="15" customWidth="1"/>
+    <col min="27" max="16384" width="10.5" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -3709,43 +3604,40 @@
         <v>214</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q1" s="30" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="R1" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="T1" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="U1" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="V1" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="S1" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="T1" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="U1" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="V1" s="12" t="s">
-        <v>232</v>
-      </c>
       <c r="W1" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="X1" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="Y1" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="X1" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y1" s="24" t="s">
+      <c r="Z1" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="Z1" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="AA1" s="14" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:26" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="36" t="s">
         <v>3</v>
       </c>
@@ -3789,46 +3681,43 @@
         <v>16</v>
       </c>
       <c r="O2" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="P2" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q2" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="R2" s="39" t="s">
+        <v>223</v>
+      </c>
+      <c r="S2" s="36" t="s">
         <v>222</v>
       </c>
-      <c r="P2" s="36" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q2" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="R2" s="39" t="s">
+      <c r="T2" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="U2" s="40" t="s">
+        <v>229</v>
+      </c>
+      <c r="V2" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="W2" s="36" t="s">
         <v>225</v>
       </c>
-      <c r="S2" s="36" t="s">
-        <v>224</v>
-      </c>
-      <c r="T2" s="36" t="s">
-        <v>223</v>
-      </c>
-      <c r="U2" s="36" t="s">
-        <v>235</v>
-      </c>
-      <c r="V2" s="40" t="s">
-        <v>231</v>
-      </c>
-      <c r="W2" s="36" t="s">
+      <c r="X2" s="41" t="s">
+        <v>227</v>
+      </c>
+      <c r="Y2" s="42" t="s">
         <v>226</v>
       </c>
-      <c r="X2" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="Y2" s="41" t="s">
-        <v>229</v>
-      </c>
-      <c r="Z2" s="42" t="s">
+      <c r="Z2" s="43" t="s">
         <v>228</v>
       </c>
-      <c r="AA2" s="43" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="53"/>
       <c r="B3" s="47"/>
       <c r="C3" s="44"/>
@@ -3852,12 +3741,11 @@
       <c r="U3" s="47"/>
       <c r="V3" s="47"/>
       <c r="W3" s="47"/>
-      <c r="X3" s="47"/>
-      <c r="Y3" s="50"/>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="52"/>
-    </row>
-    <row r="4" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X3" s="50"/>
+      <c r="Y3" s="51"/>
+      <c r="Z3" s="52"/>
+    </row>
+    <row r="4" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="54"/>
       <c r="B4" s="18"/>
       <c r="C4" s="34"/>
@@ -3881,12 +3769,11 @@
       <c r="U4" s="18"/>
       <c r="V4" s="18"/>
       <c r="W4" s="18"/>
-      <c r="X4" s="18"/>
-      <c r="Y4" s="25"/>
-      <c r="Z4" s="28"/>
-      <c r="AA4" s="23"/>
-    </row>
-    <row r="5" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X4" s="25"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="23"/>
+    </row>
+    <row r="5" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="54"/>
       <c r="B5" s="18"/>
       <c r="C5" s="34"/>
@@ -3910,12 +3797,11 @@
       <c r="U5" s="18"/>
       <c r="V5" s="18"/>
       <c r="W5" s="18"/>
-      <c r="X5" s="18"/>
-      <c r="Y5" s="25"/>
-      <c r="Z5" s="28"/>
-      <c r="AA5" s="23"/>
-    </row>
-    <row r="6" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X5" s="25"/>
+      <c r="Y5" s="28"/>
+      <c r="Z5" s="23"/>
+    </row>
+    <row r="6" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17"/>
       <c r="B6" s="18"/>
       <c r="C6" s="34"/>
@@ -3939,12 +3825,11 @@
       <c r="U6" s="18"/>
       <c r="V6" s="18"/>
       <c r="W6" s="18"/>
-      <c r="X6" s="18"/>
-      <c r="Y6" s="25"/>
-      <c r="Z6" s="28"/>
-      <c r="AA6" s="23"/>
-    </row>
-    <row r="7" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X6" s="25"/>
+      <c r="Y6" s="28"/>
+      <c r="Z6" s="23"/>
+    </row>
+    <row r="7" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="54"/>
       <c r="B7" s="18"/>
       <c r="C7" s="34"/>
@@ -3968,12 +3853,11 @@
       <c r="U7" s="18"/>
       <c r="V7" s="18"/>
       <c r="W7" s="18"/>
-      <c r="X7" s="18"/>
-      <c r="Y7" s="25"/>
-      <c r="Z7" s="28"/>
-      <c r="AA7" s="23"/>
-    </row>
-    <row r="8" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X7" s="25"/>
+      <c r="Y7" s="28"/>
+      <c r="Z7" s="23"/>
+    </row>
+    <row r="8" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="54"/>
       <c r="B8" s="18"/>
       <c r="C8" s="34"/>
@@ -3997,12 +3881,11 @@
       <c r="U8" s="18"/>
       <c r="V8" s="18"/>
       <c r="W8" s="18"/>
-      <c r="X8" s="18"/>
-      <c r="Y8" s="25"/>
-      <c r="Z8" s="28"/>
-      <c r="AA8" s="23"/>
-    </row>
-    <row r="9" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X8" s="25"/>
+      <c r="Y8" s="28"/>
+      <c r="Z8" s="23"/>
+    </row>
+    <row r="9" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="54"/>
       <c r="B9" s="18"/>
       <c r="C9" s="34"/>
@@ -4026,12 +3909,11 @@
       <c r="U9" s="18"/>
       <c r="V9" s="18"/>
       <c r="W9" s="18"/>
-      <c r="X9" s="18"/>
-      <c r="Y9" s="25"/>
-      <c r="Z9" s="28"/>
-      <c r="AA9" s="23"/>
-    </row>
-    <row r="10" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X9" s="25"/>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="23"/>
+    </row>
+    <row r="10" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17"/>
       <c r="B10" s="18"/>
       <c r="C10" s="34"/>
@@ -4055,12 +3937,11 @@
       <c r="U10" s="18"/>
       <c r="V10" s="18"/>
       <c r="W10" s="18"/>
-      <c r="X10" s="18"/>
-      <c r="Y10" s="25"/>
-      <c r="Z10" s="28"/>
-      <c r="AA10" s="23"/>
-    </row>
-    <row r="11" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X10" s="25"/>
+      <c r="Y10" s="28"/>
+      <c r="Z10" s="23"/>
+    </row>
+    <row r="11" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17"/>
       <c r="B11" s="18"/>
       <c r="C11" s="34"/>
@@ -4084,12 +3965,11 @@
       <c r="U11" s="18"/>
       <c r="V11" s="18"/>
       <c r="W11" s="18"/>
-      <c r="X11" s="18"/>
-      <c r="Y11" s="25"/>
-      <c r="Z11" s="28"/>
-      <c r="AA11" s="23"/>
-    </row>
-    <row r="12" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X11" s="25"/>
+      <c r="Y11" s="28"/>
+      <c r="Z11" s="23"/>
+    </row>
+    <row r="12" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17"/>
       <c r="B12" s="18"/>
       <c r="C12" s="34"/>
@@ -4113,12 +3993,11 @@
       <c r="U12" s="18"/>
       <c r="V12" s="18"/>
       <c r="W12" s="18"/>
-      <c r="X12" s="18"/>
-      <c r="Y12" s="25"/>
-      <c r="Z12" s="28"/>
-      <c r="AA12" s="23"/>
-    </row>
-    <row r="13" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X12" s="25"/>
+      <c r="Y12" s="28"/>
+      <c r="Z12" s="23"/>
+    </row>
+    <row r="13" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17"/>
       <c r="B13" s="18"/>
       <c r="C13" s="34"/>
@@ -4142,12 +4021,11 @@
       <c r="U13" s="18"/>
       <c r="V13" s="18"/>
       <c r="W13" s="18"/>
-      <c r="X13" s="18"/>
-      <c r="Y13" s="25"/>
-      <c r="Z13" s="28"/>
-      <c r="AA13" s="23"/>
-    </row>
-    <row r="14" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X13" s="25"/>
+      <c r="Y13" s="28"/>
+      <c r="Z13" s="23"/>
+    </row>
+    <row r="14" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17"/>
       <c r="B14" s="18"/>
       <c r="C14" s="34"/>
@@ -4171,12 +4049,11 @@
       <c r="U14" s="18"/>
       <c r="V14" s="18"/>
       <c r="W14" s="18"/>
-      <c r="X14" s="18"/>
-      <c r="Y14" s="25"/>
-      <c r="Z14" s="28"/>
-      <c r="AA14" s="23"/>
-    </row>
-    <row r="15" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X14" s="25"/>
+      <c r="Y14" s="28"/>
+      <c r="Z14" s="23"/>
+    </row>
+    <row r="15" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17"/>
       <c r="B15" s="18"/>
       <c r="C15" s="34"/>
@@ -4200,12 +4077,11 @@
       <c r="U15" s="18"/>
       <c r="V15" s="18"/>
       <c r="W15" s="18"/>
-      <c r="X15" s="18"/>
-      <c r="Y15" s="25"/>
-      <c r="Z15" s="28"/>
-      <c r="AA15" s="23"/>
-    </row>
-    <row r="16" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X15" s="25"/>
+      <c r="Y15" s="28"/>
+      <c r="Z15" s="23"/>
+    </row>
+    <row r="16" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17"/>
       <c r="B16" s="18"/>
       <c r="C16" s="34"/>
@@ -4229,12 +4105,11 @@
       <c r="U16" s="18"/>
       <c r="V16" s="18"/>
       <c r="W16" s="18"/>
-      <c r="X16" s="18"/>
-      <c r="Y16" s="25"/>
-      <c r="Z16" s="28"/>
-      <c r="AA16" s="23"/>
-    </row>
-    <row r="17" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X16" s="25"/>
+      <c r="Y16" s="28"/>
+      <c r="Z16" s="23"/>
+    </row>
+    <row r="17" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="17"/>
       <c r="B17" s="18"/>
       <c r="C17" s="34"/>
@@ -4258,12 +4133,11 @@
       <c r="U17" s="18"/>
       <c r="V17" s="18"/>
       <c r="W17" s="18"/>
-      <c r="X17" s="18"/>
-      <c r="Y17" s="25"/>
-      <c r="Z17" s="28"/>
-      <c r="AA17" s="23"/>
-    </row>
-    <row r="18" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X17" s="25"/>
+      <c r="Y17" s="28"/>
+      <c r="Z17" s="23"/>
+    </row>
+    <row r="18" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17"/>
       <c r="B18" s="18"/>
       <c r="C18" s="34"/>
@@ -4287,12 +4161,11 @@
       <c r="U18" s="18"/>
       <c r="V18" s="18"/>
       <c r="W18" s="18"/>
-      <c r="X18" s="18"/>
-      <c r="Y18" s="25"/>
-      <c r="Z18" s="28"/>
-      <c r="AA18" s="23"/>
-    </row>
-    <row r="19" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X18" s="25"/>
+      <c r="Y18" s="28"/>
+      <c r="Z18" s="23"/>
+    </row>
+    <row r="19" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17"/>
       <c r="B19" s="18"/>
       <c r="C19" s="34"/>
@@ -4316,12 +4189,11 @@
       <c r="U19" s="18"/>
       <c r="V19" s="18"/>
       <c r="W19" s="18"/>
-      <c r="X19" s="18"/>
-      <c r="Y19" s="25"/>
-      <c r="Z19" s="28"/>
-      <c r="AA19" s="23"/>
-    </row>
-    <row r="20" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X19" s="25"/>
+      <c r="Y19" s="28"/>
+      <c r="Z19" s="23"/>
+    </row>
+    <row r="20" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17"/>
       <c r="B20" s="18"/>
       <c r="C20" s="34"/>
@@ -4345,12 +4217,11 @@
       <c r="U20" s="18"/>
       <c r="V20" s="18"/>
       <c r="W20" s="18"/>
-      <c r="X20" s="18"/>
-      <c r="Y20" s="25"/>
-      <c r="Z20" s="28"/>
-      <c r="AA20" s="23"/>
-    </row>
-    <row r="21" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X20" s="25"/>
+      <c r="Y20" s="28"/>
+      <c r="Z20" s="23"/>
+    </row>
+    <row r="21" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17"/>
       <c r="B21" s="18"/>
       <c r="C21" s="34"/>
@@ -4374,12 +4245,11 @@
       <c r="U21" s="18"/>
       <c r="V21" s="18"/>
       <c r="W21" s="18"/>
-      <c r="X21" s="18"/>
-      <c r="Y21" s="25"/>
-      <c r="Z21" s="28"/>
-      <c r="AA21" s="23"/>
-    </row>
-    <row r="22" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X21" s="25"/>
+      <c r="Y21" s="28"/>
+      <c r="Z21" s="23"/>
+    </row>
+    <row r="22" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="17"/>
       <c r="B22" s="18"/>
       <c r="C22" s="34"/>
@@ -4403,12 +4273,11 @@
       <c r="U22" s="18"/>
       <c r="V22" s="18"/>
       <c r="W22" s="18"/>
-      <c r="X22" s="18"/>
-      <c r="Y22" s="25"/>
-      <c r="Z22" s="28"/>
-      <c r="AA22" s="23"/>
-    </row>
-    <row r="23" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X22" s="25"/>
+      <c r="Y22" s="28"/>
+      <c r="Z22" s="23"/>
+    </row>
+    <row r="23" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17"/>
       <c r="B23" s="18"/>
       <c r="C23" s="34"/>
@@ -4432,12 +4301,11 @@
       <c r="U23" s="18"/>
       <c r="V23" s="18"/>
       <c r="W23" s="18"/>
-      <c r="X23" s="18"/>
-      <c r="Y23" s="25"/>
-      <c r="Z23" s="28"/>
-      <c r="AA23" s="23"/>
-    </row>
-    <row r="24" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X23" s="25"/>
+      <c r="Y23" s="28"/>
+      <c r="Z23" s="23"/>
+    </row>
+    <row r="24" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17"/>
       <c r="B24" s="18"/>
       <c r="C24" s="34"/>
@@ -4461,12 +4329,11 @@
       <c r="U24" s="18"/>
       <c r="V24" s="18"/>
       <c r="W24" s="18"/>
-      <c r="X24" s="18"/>
-      <c r="Y24" s="25"/>
-      <c r="Z24" s="28"/>
-      <c r="AA24" s="23"/>
-    </row>
-    <row r="25" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X24" s="25"/>
+      <c r="Y24" s="28"/>
+      <c r="Z24" s="23"/>
+    </row>
+    <row r="25" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="17"/>
       <c r="B25" s="18"/>
       <c r="C25" s="34"/>
@@ -4490,12 +4357,11 @@
       <c r="U25" s="18"/>
       <c r="V25" s="18"/>
       <c r="W25" s="18"/>
-      <c r="X25" s="18"/>
-      <c r="Y25" s="25"/>
-      <c r="Z25" s="28"/>
-      <c r="AA25" s="23"/>
-    </row>
-    <row r="26" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X25" s="25"/>
+      <c r="Y25" s="28"/>
+      <c r="Z25" s="23"/>
+    </row>
+    <row r="26" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17"/>
       <c r="B26" s="18"/>
       <c r="C26" s="34"/>
@@ -4519,12 +4385,11 @@
       <c r="U26" s="18"/>
       <c r="V26" s="18"/>
       <c r="W26" s="18"/>
-      <c r="X26" s="18"/>
-      <c r="Y26" s="25"/>
-      <c r="Z26" s="28"/>
-      <c r="AA26" s="23"/>
-    </row>
-    <row r="27" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X26" s="25"/>
+      <c r="Y26" s="28"/>
+      <c r="Z26" s="23"/>
+    </row>
+    <row r="27" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
       <c r="B27" s="18"/>
       <c r="C27" s="34"/>
@@ -4548,12 +4413,11 @@
       <c r="U27" s="18"/>
       <c r="V27" s="18"/>
       <c r="W27" s="18"/>
-      <c r="X27" s="18"/>
-      <c r="Y27" s="25"/>
-      <c r="Z27" s="28"/>
-      <c r="AA27" s="23"/>
-    </row>
-    <row r="28" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X27" s="25"/>
+      <c r="Y27" s="28"/>
+      <c r="Z27" s="23"/>
+    </row>
+    <row r="28" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17"/>
       <c r="B28" s="18"/>
       <c r="C28" s="34"/>
@@ -4577,12 +4441,11 @@
       <c r="U28" s="18"/>
       <c r="V28" s="18"/>
       <c r="W28" s="18"/>
-      <c r="X28" s="18"/>
-      <c r="Y28" s="25"/>
-      <c r="Z28" s="28"/>
-      <c r="AA28" s="23"/>
-    </row>
-    <row r="29" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X28" s="25"/>
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="23"/>
+    </row>
+    <row r="29" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="17"/>
       <c r="B29" s="18"/>
       <c r="C29" s="34"/>
@@ -4606,12 +4469,11 @@
       <c r="U29" s="18"/>
       <c r="V29" s="18"/>
       <c r="W29" s="18"/>
-      <c r="X29" s="18"/>
-      <c r="Y29" s="25"/>
-      <c r="Z29" s="28"/>
-      <c r="AA29" s="23"/>
-    </row>
-    <row r="30" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X29" s="25"/>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="23"/>
+    </row>
+    <row r="30" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="17"/>
       <c r="B30" s="18"/>
       <c r="C30" s="34"/>
@@ -4635,12 +4497,11 @@
       <c r="U30" s="18"/>
       <c r="V30" s="18"/>
       <c r="W30" s="18"/>
-      <c r="X30" s="18"/>
-      <c r="Y30" s="25"/>
-      <c r="Z30" s="28"/>
-      <c r="AA30" s="23"/>
-    </row>
-    <row r="31" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X30" s="25"/>
+      <c r="Y30" s="28"/>
+      <c r="Z30" s="23"/>
+    </row>
+    <row r="31" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="17"/>
       <c r="B31" s="18"/>
       <c r="C31" s="34"/>
@@ -4664,12 +4525,11 @@
       <c r="U31" s="18"/>
       <c r="V31" s="18"/>
       <c r="W31" s="18"/>
-      <c r="X31" s="18"/>
-      <c r="Y31" s="25"/>
-      <c r="Z31" s="28"/>
-      <c r="AA31" s="23"/>
-    </row>
-    <row r="32" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X31" s="25"/>
+      <c r="Y31" s="28"/>
+      <c r="Z31" s="23"/>
+    </row>
+    <row r="32" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="17"/>
       <c r="B32" s="18"/>
       <c r="C32" s="34"/>
@@ -4693,12 +4553,11 @@
       <c r="U32" s="18"/>
       <c r="V32" s="18"/>
       <c r="W32" s="18"/>
-      <c r="X32" s="18"/>
-      <c r="Y32" s="25"/>
-      <c r="Z32" s="28"/>
-      <c r="AA32" s="23"/>
-    </row>
-    <row r="33" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X32" s="25"/>
+      <c r="Y32" s="28"/>
+      <c r="Z32" s="23"/>
+    </row>
+    <row r="33" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="17"/>
       <c r="B33" s="18"/>
       <c r="C33" s="34"/>
@@ -4722,12 +4581,11 @@
       <c r="U33" s="18"/>
       <c r="V33" s="18"/>
       <c r="W33" s="18"/>
-      <c r="X33" s="18"/>
-      <c r="Y33" s="25"/>
-      <c r="Z33" s="28"/>
-      <c r="AA33" s="23"/>
-    </row>
-    <row r="34" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X33" s="25"/>
+      <c r="Y33" s="28"/>
+      <c r="Z33" s="23"/>
+    </row>
+    <row r="34" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="17"/>
       <c r="B34" s="18"/>
       <c r="C34" s="34"/>
@@ -4751,12 +4609,11 @@
       <c r="U34" s="18"/>
       <c r="V34" s="18"/>
       <c r="W34" s="18"/>
-      <c r="X34" s="18"/>
-      <c r="Y34" s="25"/>
-      <c r="Z34" s="28"/>
-      <c r="AA34" s="23"/>
-    </row>
-    <row r="35" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X34" s="25"/>
+      <c r="Y34" s="28"/>
+      <c r="Z34" s="23"/>
+    </row>
+    <row r="35" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="17"/>
       <c r="B35" s="18"/>
       <c r="C35" s="34"/>
@@ -4780,12 +4637,11 @@
       <c r="U35" s="18"/>
       <c r="V35" s="18"/>
       <c r="W35" s="18"/>
-      <c r="X35" s="18"/>
-      <c r="Y35" s="25"/>
-      <c r="Z35" s="28"/>
-      <c r="AA35" s="23"/>
-    </row>
-    <row r="36" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X35" s="25"/>
+      <c r="Y35" s="28"/>
+      <c r="Z35" s="23"/>
+    </row>
+    <row r="36" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="17"/>
       <c r="B36" s="18"/>
       <c r="C36" s="34"/>
@@ -4809,12 +4665,11 @@
       <c r="U36" s="18"/>
       <c r="V36" s="18"/>
       <c r="W36" s="18"/>
-      <c r="X36" s="18"/>
-      <c r="Y36" s="25"/>
-      <c r="Z36" s="28"/>
-      <c r="AA36" s="23"/>
-    </row>
-    <row r="37" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X36" s="25"/>
+      <c r="Y36" s="28"/>
+      <c r="Z36" s="23"/>
+    </row>
+    <row r="37" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="17"/>
       <c r="B37" s="18"/>
       <c r="C37" s="34"/>
@@ -4838,12 +4693,11 @@
       <c r="U37" s="18"/>
       <c r="V37" s="18"/>
       <c r="W37" s="18"/>
-      <c r="X37" s="18"/>
-      <c r="Y37" s="25"/>
-      <c r="Z37" s="28"/>
-      <c r="AA37" s="23"/>
-    </row>
-    <row r="38" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X37" s="25"/>
+      <c r="Y37" s="28"/>
+      <c r="Z37" s="23"/>
+    </row>
+    <row r="38" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="17"/>
       <c r="B38" s="18"/>
       <c r="C38" s="34"/>
@@ -4867,12 +4721,11 @@
       <c r="U38" s="18"/>
       <c r="V38" s="18"/>
       <c r="W38" s="18"/>
-      <c r="X38" s="18"/>
-      <c r="Y38" s="25"/>
-      <c r="Z38" s="28"/>
-      <c r="AA38" s="23"/>
-    </row>
-    <row r="39" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X38" s="25"/>
+      <c r="Y38" s="28"/>
+      <c r="Z38" s="23"/>
+    </row>
+    <row r="39" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="17"/>
       <c r="B39" s="18"/>
       <c r="C39" s="34"/>
@@ -4896,12 +4749,11 @@
       <c r="U39" s="18"/>
       <c r="V39" s="18"/>
       <c r="W39" s="18"/>
-      <c r="X39" s="18"/>
-      <c r="Y39" s="25"/>
-      <c r="Z39" s="28"/>
-      <c r="AA39" s="23"/>
-    </row>
-    <row r="40" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X39" s="25"/>
+      <c r="Y39" s="28"/>
+      <c r="Z39" s="23"/>
+    </row>
+    <row r="40" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="17"/>
       <c r="B40" s="18"/>
       <c r="C40" s="34"/>
@@ -4925,12 +4777,11 @@
       <c r="U40" s="18"/>
       <c r="V40" s="18"/>
       <c r="W40" s="18"/>
-      <c r="X40" s="18"/>
-      <c r="Y40" s="25"/>
-      <c r="Z40" s="28"/>
-      <c r="AA40" s="23"/>
-    </row>
-    <row r="41" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X40" s="25"/>
+      <c r="Y40" s="28"/>
+      <c r="Z40" s="23"/>
+    </row>
+    <row r="41" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="17"/>
       <c r="B41" s="18"/>
       <c r="C41" s="34"/>
@@ -4954,12 +4805,11 @@
       <c r="U41" s="18"/>
       <c r="V41" s="18"/>
       <c r="W41" s="18"/>
-      <c r="X41" s="18"/>
-      <c r="Y41" s="25"/>
-      <c r="Z41" s="28"/>
-      <c r="AA41" s="23"/>
-    </row>
-    <row r="42" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X41" s="25"/>
+      <c r="Y41" s="28"/>
+      <c r="Z41" s="23"/>
+    </row>
+    <row r="42" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="17"/>
       <c r="B42" s="18"/>
       <c r="C42" s="34"/>
@@ -4983,12 +4833,11 @@
       <c r="U42" s="18"/>
       <c r="V42" s="18"/>
       <c r="W42" s="18"/>
-      <c r="X42" s="18"/>
-      <c r="Y42" s="25"/>
-      <c r="Z42" s="28"/>
-      <c r="AA42" s="23"/>
-    </row>
-    <row r="43" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X42" s="25"/>
+      <c r="Y42" s="28"/>
+      <c r="Z42" s="23"/>
+    </row>
+    <row r="43" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="17"/>
       <c r="B43" s="18"/>
       <c r="C43" s="34"/>
@@ -5012,12 +4861,11 @@
       <c r="U43" s="18"/>
       <c r="V43" s="18"/>
       <c r="W43" s="18"/>
-      <c r="X43" s="18"/>
-      <c r="Y43" s="25"/>
-      <c r="Z43" s="28"/>
-      <c r="AA43" s="23"/>
-    </row>
-    <row r="44" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X43" s="25"/>
+      <c r="Y43" s="28"/>
+      <c r="Z43" s="23"/>
+    </row>
+    <row r="44" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="17"/>
       <c r="B44" s="18"/>
       <c r="C44" s="34"/>
@@ -5041,12 +4889,11 @@
       <c r="U44" s="18"/>
       <c r="V44" s="18"/>
       <c r="W44" s="18"/>
-      <c r="X44" s="18"/>
-      <c r="Y44" s="25"/>
-      <c r="Z44" s="28"/>
-      <c r="AA44" s="23"/>
-    </row>
-    <row r="45" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X44" s="25"/>
+      <c r="Y44" s="28"/>
+      <c r="Z44" s="23"/>
+    </row>
+    <row r="45" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="17"/>
       <c r="B45" s="18"/>
       <c r="C45" s="34"/>
@@ -5070,12 +4917,11 @@
       <c r="U45" s="18"/>
       <c r="V45" s="18"/>
       <c r="W45" s="18"/>
-      <c r="X45" s="18"/>
-      <c r="Y45" s="25"/>
-      <c r="Z45" s="28"/>
-      <c r="AA45" s="23"/>
-    </row>
-    <row r="46" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X45" s="25"/>
+      <c r="Y45" s="28"/>
+      <c r="Z45" s="23"/>
+    </row>
+    <row r="46" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="17"/>
       <c r="B46" s="18"/>
       <c r="C46" s="34"/>
@@ -5099,12 +4945,11 @@
       <c r="U46" s="18"/>
       <c r="V46" s="18"/>
       <c r="W46" s="18"/>
-      <c r="X46" s="18"/>
-      <c r="Y46" s="25"/>
-      <c r="Z46" s="28"/>
-      <c r="AA46" s="23"/>
-    </row>
-    <row r="47" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X46" s="25"/>
+      <c r="Y46" s="28"/>
+      <c r="Z46" s="23"/>
+    </row>
+    <row r="47" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="17"/>
       <c r="B47" s="18"/>
       <c r="C47" s="34"/>
@@ -5128,12 +4973,11 @@
       <c r="U47" s="18"/>
       <c r="V47" s="18"/>
       <c r="W47" s="18"/>
-      <c r="X47" s="18"/>
-      <c r="Y47" s="25"/>
-      <c r="Z47" s="28"/>
-      <c r="AA47" s="23"/>
-    </row>
-    <row r="48" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X47" s="25"/>
+      <c r="Y47" s="28"/>
+      <c r="Z47" s="23"/>
+    </row>
+    <row r="48" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="17"/>
       <c r="B48" s="18"/>
       <c r="C48" s="34"/>
@@ -5157,12 +5001,11 @@
       <c r="U48" s="18"/>
       <c r="V48" s="18"/>
       <c r="W48" s="18"/>
-      <c r="X48" s="18"/>
-      <c r="Y48" s="25"/>
-      <c r="Z48" s="28"/>
-      <c r="AA48" s="23"/>
-    </row>
-    <row r="49" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X48" s="25"/>
+      <c r="Y48" s="28"/>
+      <c r="Z48" s="23"/>
+    </row>
+    <row r="49" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="17"/>
       <c r="B49" s="18"/>
       <c r="C49" s="34"/>
@@ -5186,12 +5029,11 @@
       <c r="U49" s="18"/>
       <c r="V49" s="18"/>
       <c r="W49" s="18"/>
-      <c r="X49" s="18"/>
-      <c r="Y49" s="25"/>
-      <c r="Z49" s="28"/>
-      <c r="AA49" s="23"/>
-    </row>
-    <row r="50" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X49" s="25"/>
+      <c r="Y49" s="28"/>
+      <c r="Z49" s="23"/>
+    </row>
+    <row r="50" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="17"/>
       <c r="B50" s="18"/>
       <c r="C50" s="34"/>
@@ -5215,12 +5057,11 @@
       <c r="U50" s="18"/>
       <c r="V50" s="18"/>
       <c r="W50" s="18"/>
-      <c r="X50" s="18"/>
-      <c r="Y50" s="25"/>
-      <c r="Z50" s="28"/>
-      <c r="AA50" s="23"/>
-    </row>
-    <row r="51" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X50" s="25"/>
+      <c r="Y50" s="28"/>
+      <c r="Z50" s="23"/>
+    </row>
+    <row r="51" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="17"/>
       <c r="B51" s="18"/>
       <c r="C51" s="34"/>
@@ -5244,12 +5085,11 @@
       <c r="U51" s="18"/>
       <c r="V51" s="18"/>
       <c r="W51" s="18"/>
-      <c r="X51" s="18"/>
-      <c r="Y51" s="25"/>
-      <c r="Z51" s="28"/>
-      <c r="AA51" s="23"/>
-    </row>
-    <row r="52" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X51" s="25"/>
+      <c r="Y51" s="28"/>
+      <c r="Z51" s="23"/>
+    </row>
+    <row r="52" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="17"/>
       <c r="B52" s="18"/>
       <c r="C52" s="34"/>
@@ -5273,12 +5113,11 @@
       <c r="U52" s="18"/>
       <c r="V52" s="18"/>
       <c r="W52" s="18"/>
-      <c r="X52" s="18"/>
-      <c r="Y52" s="25"/>
-      <c r="Z52" s="28"/>
-      <c r="AA52" s="23"/>
-    </row>
-    <row r="53" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X52" s="25"/>
+      <c r="Y52" s="28"/>
+      <c r="Z52" s="23"/>
+    </row>
+    <row r="53" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="17"/>
       <c r="B53" s="18"/>
       <c r="C53" s="34"/>
@@ -5302,12 +5141,11 @@
       <c r="U53" s="18"/>
       <c r="V53" s="18"/>
       <c r="W53" s="18"/>
-      <c r="X53" s="18"/>
-      <c r="Y53" s="25"/>
-      <c r="Z53" s="28"/>
-      <c r="AA53" s="23"/>
-    </row>
-    <row r="54" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X53" s="25"/>
+      <c r="Y53" s="28"/>
+      <c r="Z53" s="23"/>
+    </row>
+    <row r="54" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="17"/>
       <c r="B54" s="18"/>
       <c r="C54" s="34"/>
@@ -5331,12 +5169,11 @@
       <c r="U54" s="18"/>
       <c r="V54" s="18"/>
       <c r="W54" s="18"/>
-      <c r="X54" s="18"/>
-      <c r="Y54" s="25"/>
-      <c r="Z54" s="28"/>
-      <c r="AA54" s="23"/>
-    </row>
-    <row r="55" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X54" s="25"/>
+      <c r="Y54" s="28"/>
+      <c r="Z54" s="23"/>
+    </row>
+    <row r="55" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="17"/>
       <c r="B55" s="18"/>
       <c r="C55" s="34"/>
@@ -5360,12 +5197,11 @@
       <c r="U55" s="18"/>
       <c r="V55" s="18"/>
       <c r="W55" s="18"/>
-      <c r="X55" s="18"/>
-      <c r="Y55" s="25"/>
-      <c r="Z55" s="28"/>
-      <c r="AA55" s="23"/>
-    </row>
-    <row r="56" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X55" s="25"/>
+      <c r="Y55" s="28"/>
+      <c r="Z55" s="23"/>
+    </row>
+    <row r="56" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="17"/>
       <c r="B56" s="18"/>
       <c r="C56" s="34"/>
@@ -5389,12 +5225,11 @@
       <c r="U56" s="18"/>
       <c r="V56" s="18"/>
       <c r="W56" s="18"/>
-      <c r="X56" s="18"/>
-      <c r="Y56" s="25"/>
-      <c r="Z56" s="28"/>
-      <c r="AA56" s="23"/>
-    </row>
-    <row r="57" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X56" s="25"/>
+      <c r="Y56" s="28"/>
+      <c r="Z56" s="23"/>
+    </row>
+    <row r="57" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="17"/>
       <c r="B57" s="18"/>
       <c r="C57" s="34"/>
@@ -5418,12 +5253,11 @@
       <c r="U57" s="18"/>
       <c r="V57" s="18"/>
       <c r="W57" s="18"/>
-      <c r="X57" s="18"/>
-      <c r="Y57" s="25"/>
-      <c r="Z57" s="28"/>
-      <c r="AA57" s="23"/>
-    </row>
-    <row r="58" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X57" s="25"/>
+      <c r="Y57" s="28"/>
+      <c r="Z57" s="23"/>
+    </row>
+    <row r="58" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="17"/>
       <c r="B58" s="18"/>
       <c r="C58" s="34"/>
@@ -5447,12 +5281,11 @@
       <c r="U58" s="18"/>
       <c r="V58" s="18"/>
       <c r="W58" s="18"/>
-      <c r="X58" s="18"/>
-      <c r="Y58" s="25"/>
-      <c r="Z58" s="28"/>
-      <c r="AA58" s="23"/>
-    </row>
-    <row r="59" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X58" s="25"/>
+      <c r="Y58" s="28"/>
+      <c r="Z58" s="23"/>
+    </row>
+    <row r="59" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="17"/>
       <c r="B59" s="18"/>
       <c r="C59" s="34"/>
@@ -5476,12 +5309,11 @@
       <c r="U59" s="18"/>
       <c r="V59" s="18"/>
       <c r="W59" s="18"/>
-      <c r="X59" s="18"/>
-      <c r="Y59" s="25"/>
-      <c r="Z59" s="28"/>
-      <c r="AA59" s="23"/>
-    </row>
-    <row r="60" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X59" s="25"/>
+      <c r="Y59" s="28"/>
+      <c r="Z59" s="23"/>
+    </row>
+    <row r="60" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="17"/>
       <c r="B60" s="18"/>
       <c r="C60" s="34"/>
@@ -5505,12 +5337,11 @@
       <c r="U60" s="18"/>
       <c r="V60" s="18"/>
       <c r="W60" s="18"/>
-      <c r="X60" s="18"/>
-      <c r="Y60" s="25"/>
-      <c r="Z60" s="28"/>
-      <c r="AA60" s="23"/>
-    </row>
-    <row r="61" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X60" s="25"/>
+      <c r="Y60" s="28"/>
+      <c r="Z60" s="23"/>
+    </row>
+    <row r="61" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="17"/>
       <c r="B61" s="18"/>
       <c r="C61" s="34"/>
@@ -5534,12 +5365,11 @@
       <c r="U61" s="18"/>
       <c r="V61" s="18"/>
       <c r="W61" s="18"/>
-      <c r="X61" s="18"/>
-      <c r="Y61" s="25"/>
-      <c r="Z61" s="28"/>
-      <c r="AA61" s="23"/>
-    </row>
-    <row r="62" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X61" s="25"/>
+      <c r="Y61" s="28"/>
+      <c r="Z61" s="23"/>
+    </row>
+    <row r="62" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="17"/>
       <c r="B62" s="18"/>
       <c r="C62" s="34"/>
@@ -5563,12 +5393,11 @@
       <c r="U62" s="18"/>
       <c r="V62" s="18"/>
       <c r="W62" s="18"/>
-      <c r="X62" s="18"/>
-      <c r="Y62" s="25"/>
-      <c r="Z62" s="28"/>
-      <c r="AA62" s="23"/>
-    </row>
-    <row r="63" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X62" s="25"/>
+      <c r="Y62" s="28"/>
+      <c r="Z62" s="23"/>
+    </row>
+    <row r="63" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="17"/>
       <c r="B63" s="18"/>
       <c r="C63" s="34"/>
@@ -5592,12 +5421,11 @@
       <c r="U63" s="18"/>
       <c r="V63" s="18"/>
       <c r="W63" s="18"/>
-      <c r="X63" s="18"/>
-      <c r="Y63" s="25"/>
-      <c r="Z63" s="28"/>
-      <c r="AA63" s="23"/>
-    </row>
-    <row r="64" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X63" s="25"/>
+      <c r="Y63" s="28"/>
+      <c r="Z63" s="23"/>
+    </row>
+    <row r="64" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="17"/>
       <c r="B64" s="18"/>
       <c r="C64" s="34"/>
@@ -5621,12 +5449,11 @@
       <c r="U64" s="18"/>
       <c r="V64" s="18"/>
       <c r="W64" s="18"/>
-      <c r="X64" s="18"/>
-      <c r="Y64" s="25"/>
-      <c r="Z64" s="28"/>
-      <c r="AA64" s="23"/>
-    </row>
-    <row r="65" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X64" s="25"/>
+      <c r="Y64" s="28"/>
+      <c r="Z64" s="23"/>
+    </row>
+    <row r="65" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="17"/>
       <c r="B65" s="18"/>
       <c r="C65" s="34"/>
@@ -5650,12 +5477,11 @@
       <c r="U65" s="18"/>
       <c r="V65" s="18"/>
       <c r="W65" s="18"/>
-      <c r="X65" s="18"/>
-      <c r="Y65" s="25"/>
-      <c r="Z65" s="28"/>
-      <c r="AA65" s="23"/>
-    </row>
-    <row r="66" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X65" s="25"/>
+      <c r="Y65" s="28"/>
+      <c r="Z65" s="23"/>
+    </row>
+    <row r="66" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="17"/>
       <c r="B66" s="18"/>
       <c r="C66" s="34"/>
@@ -5679,12 +5505,11 @@
       <c r="U66" s="18"/>
       <c r="V66" s="18"/>
       <c r="W66" s="18"/>
-      <c r="X66" s="18"/>
-      <c r="Y66" s="25"/>
-      <c r="Z66" s="28"/>
-      <c r="AA66" s="23"/>
-    </row>
-    <row r="67" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X66" s="25"/>
+      <c r="Y66" s="28"/>
+      <c r="Z66" s="23"/>
+    </row>
+    <row r="67" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="17"/>
       <c r="B67" s="18"/>
       <c r="C67" s="34"/>
@@ -5708,12 +5533,11 @@
       <c r="U67" s="18"/>
       <c r="V67" s="18"/>
       <c r="W67" s="18"/>
-      <c r="X67" s="18"/>
-      <c r="Y67" s="25"/>
-      <c r="Z67" s="28"/>
-      <c r="AA67" s="23"/>
-    </row>
-    <row r="68" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X67" s="25"/>
+      <c r="Y67" s="28"/>
+      <c r="Z67" s="23"/>
+    </row>
+    <row r="68" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="17"/>
       <c r="B68" s="18"/>
       <c r="C68" s="34"/>
@@ -5737,12 +5561,11 @@
       <c r="U68" s="18"/>
       <c r="V68" s="18"/>
       <c r="W68" s="18"/>
-      <c r="X68" s="18"/>
-      <c r="Y68" s="25"/>
-      <c r="Z68" s="28"/>
-      <c r="AA68" s="23"/>
-    </row>
-    <row r="69" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X68" s="25"/>
+      <c r="Y68" s="28"/>
+      <c r="Z68" s="23"/>
+    </row>
+    <row r="69" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="17"/>
       <c r="B69" s="18"/>
       <c r="C69" s="34"/>
@@ -5766,12 +5589,11 @@
       <c r="U69" s="18"/>
       <c r="V69" s="18"/>
       <c r="W69" s="18"/>
-      <c r="X69" s="18"/>
-      <c r="Y69" s="25"/>
-      <c r="Z69" s="28"/>
-      <c r="AA69" s="23"/>
-    </row>
-    <row r="70" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X69" s="25"/>
+      <c r="Y69" s="28"/>
+      <c r="Z69" s="23"/>
+    </row>
+    <row r="70" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="17"/>
       <c r="B70" s="18"/>
       <c r="C70" s="34"/>
@@ -5795,12 +5617,11 @@
       <c r="U70" s="18"/>
       <c r="V70" s="18"/>
       <c r="W70" s="18"/>
-      <c r="X70" s="18"/>
-      <c r="Y70" s="25"/>
-      <c r="Z70" s="28"/>
-      <c r="AA70" s="23"/>
-    </row>
-    <row r="71" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X70" s="25"/>
+      <c r="Y70" s="28"/>
+      <c r="Z70" s="23"/>
+    </row>
+    <row r="71" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="17"/>
       <c r="B71" s="18"/>
       <c r="C71" s="34"/>
@@ -5824,12 +5645,11 @@
       <c r="U71" s="18"/>
       <c r="V71" s="18"/>
       <c r="W71" s="18"/>
-      <c r="X71" s="18"/>
-      <c r="Y71" s="25"/>
-      <c r="Z71" s="28"/>
-      <c r="AA71" s="23"/>
-    </row>
-    <row r="72" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X71" s="25"/>
+      <c r="Y71" s="28"/>
+      <c r="Z71" s="23"/>
+    </row>
+    <row r="72" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="17"/>
       <c r="B72" s="18"/>
       <c r="C72" s="34"/>
@@ -5853,12 +5673,11 @@
       <c r="U72" s="18"/>
       <c r="V72" s="18"/>
       <c r="W72" s="18"/>
-      <c r="X72" s="18"/>
-      <c r="Y72" s="25"/>
-      <c r="Z72" s="28"/>
-      <c r="AA72" s="23"/>
-    </row>
-    <row r="73" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X72" s="25"/>
+      <c r="Y72" s="28"/>
+      <c r="Z72" s="23"/>
+    </row>
+    <row r="73" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="17"/>
       <c r="B73" s="18"/>
       <c r="C73" s="34"/>
@@ -5882,12 +5701,11 @@
       <c r="U73" s="18"/>
       <c r="V73" s="18"/>
       <c r="W73" s="18"/>
-      <c r="X73" s="18"/>
-      <c r="Y73" s="25"/>
-      <c r="Z73" s="28"/>
-      <c r="AA73" s="23"/>
-    </row>
-    <row r="74" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X73" s="25"/>
+      <c r="Y73" s="28"/>
+      <c r="Z73" s="23"/>
+    </row>
+    <row r="74" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="17"/>
       <c r="B74" s="18"/>
       <c r="C74" s="34"/>
@@ -5911,12 +5729,11 @@
       <c r="U74" s="18"/>
       <c r="V74" s="18"/>
       <c r="W74" s="18"/>
-      <c r="X74" s="18"/>
-      <c r="Y74" s="25"/>
-      <c r="Z74" s="28"/>
-      <c r="AA74" s="23"/>
-    </row>
-    <row r="75" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X74" s="25"/>
+      <c r="Y74" s="28"/>
+      <c r="Z74" s="23"/>
+    </row>
+    <row r="75" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="17"/>
       <c r="B75" s="18"/>
       <c r="C75" s="34"/>
@@ -5940,12 +5757,11 @@
       <c r="U75" s="18"/>
       <c r="V75" s="18"/>
       <c r="W75" s="18"/>
-      <c r="X75" s="18"/>
-      <c r="Y75" s="25"/>
-      <c r="Z75" s="28"/>
-      <c r="AA75" s="23"/>
-    </row>
-    <row r="76" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X75" s="25"/>
+      <c r="Y75" s="28"/>
+      <c r="Z75" s="23"/>
+    </row>
+    <row r="76" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="17"/>
       <c r="B76" s="18"/>
       <c r="C76" s="34"/>
@@ -5969,12 +5785,11 @@
       <c r="U76" s="18"/>
       <c r="V76" s="18"/>
       <c r="W76" s="18"/>
-      <c r="X76" s="18"/>
-      <c r="Y76" s="25"/>
-      <c r="Z76" s="28"/>
-      <c r="AA76" s="23"/>
-    </row>
-    <row r="77" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X76" s="25"/>
+      <c r="Y76" s="28"/>
+      <c r="Z76" s="23"/>
+    </row>
+    <row r="77" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="17"/>
       <c r="B77" s="18"/>
       <c r="C77" s="34"/>
@@ -5998,12 +5813,11 @@
       <c r="U77" s="18"/>
       <c r="V77" s="18"/>
       <c r="W77" s="18"/>
-      <c r="X77" s="18"/>
-      <c r="Y77" s="25"/>
-      <c r="Z77" s="28"/>
-      <c r="AA77" s="23"/>
-    </row>
-    <row r="78" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X77" s="25"/>
+      <c r="Y77" s="28"/>
+      <c r="Z77" s="23"/>
+    </row>
+    <row r="78" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="17"/>
       <c r="B78" s="18"/>
       <c r="C78" s="34"/>
@@ -6027,12 +5841,11 @@
       <c r="U78" s="18"/>
       <c r="V78" s="18"/>
       <c r="W78" s="18"/>
-      <c r="X78" s="18"/>
-      <c r="Y78" s="25"/>
-      <c r="Z78" s="28"/>
-      <c r="AA78" s="23"/>
-    </row>
-    <row r="79" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X78" s="25"/>
+      <c r="Y78" s="28"/>
+      <c r="Z78" s="23"/>
+    </row>
+    <row r="79" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="17"/>
       <c r="B79" s="18"/>
       <c r="C79" s="34"/>
@@ -6056,12 +5869,11 @@
       <c r="U79" s="18"/>
       <c r="V79" s="18"/>
       <c r="W79" s="18"/>
-      <c r="X79" s="18"/>
-      <c r="Y79" s="25"/>
-      <c r="Z79" s="28"/>
-      <c r="AA79" s="23"/>
-    </row>
-    <row r="80" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X79" s="25"/>
+      <c r="Y79" s="28"/>
+      <c r="Z79" s="23"/>
+    </row>
+    <row r="80" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="17"/>
       <c r="B80" s="18"/>
       <c r="C80" s="34"/>
@@ -6085,12 +5897,11 @@
       <c r="U80" s="18"/>
       <c r="V80" s="18"/>
       <c r="W80" s="18"/>
-      <c r="X80" s="18"/>
-      <c r="Y80" s="25"/>
-      <c r="Z80" s="28"/>
-      <c r="AA80" s="23"/>
-    </row>
-    <row r="81" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X80" s="25"/>
+      <c r="Y80" s="28"/>
+      <c r="Z80" s="23"/>
+    </row>
+    <row r="81" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="17"/>
       <c r="B81" s="18"/>
       <c r="C81" s="34"/>
@@ -6114,12 +5925,11 @@
       <c r="U81" s="18"/>
       <c r="V81" s="18"/>
       <c r="W81" s="18"/>
-      <c r="X81" s="18"/>
-      <c r="Y81" s="25"/>
-      <c r="Z81" s="28"/>
-      <c r="AA81" s="23"/>
-    </row>
-    <row r="82" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X81" s="25"/>
+      <c r="Y81" s="28"/>
+      <c r="Z81" s="23"/>
+    </row>
+    <row r="82" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="17"/>
       <c r="B82" s="18"/>
       <c r="C82" s="34"/>
@@ -6143,12 +5953,11 @@
       <c r="U82" s="18"/>
       <c r="V82" s="18"/>
       <c r="W82" s="18"/>
-      <c r="X82" s="18"/>
-      <c r="Y82" s="25"/>
-      <c r="Z82" s="28"/>
-      <c r="AA82" s="23"/>
-    </row>
-    <row r="83" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X82" s="25"/>
+      <c r="Y82" s="28"/>
+      <c r="Z82" s="23"/>
+    </row>
+    <row r="83" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="17"/>
       <c r="B83" s="18"/>
       <c r="C83" s="34"/>
@@ -6172,12 +5981,11 @@
       <c r="U83" s="18"/>
       <c r="V83" s="18"/>
       <c r="W83" s="18"/>
-      <c r="X83" s="18"/>
-      <c r="Y83" s="25"/>
-      <c r="Z83" s="28"/>
-      <c r="AA83" s="23"/>
-    </row>
-    <row r="84" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X83" s="25"/>
+      <c r="Y83" s="28"/>
+      <c r="Z83" s="23"/>
+    </row>
+    <row r="84" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="17"/>
       <c r="B84" s="18"/>
       <c r="C84" s="34"/>
@@ -6201,12 +6009,11 @@
       <c r="U84" s="18"/>
       <c r="V84" s="18"/>
       <c r="W84" s="18"/>
-      <c r="X84" s="18"/>
-      <c r="Y84" s="25"/>
-      <c r="Z84" s="28"/>
-      <c r="AA84" s="23"/>
-    </row>
-    <row r="85" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X84" s="25"/>
+      <c r="Y84" s="28"/>
+      <c r="Z84" s="23"/>
+    </row>
+    <row r="85" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="17"/>
       <c r="B85" s="18"/>
       <c r="C85" s="34"/>
@@ -6230,12 +6037,11 @@
       <c r="U85" s="18"/>
       <c r="V85" s="18"/>
       <c r="W85" s="18"/>
-      <c r="X85" s="18"/>
-      <c r="Y85" s="25"/>
-      <c r="Z85" s="28"/>
-      <c r="AA85" s="23"/>
-    </row>
-    <row r="86" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X85" s="25"/>
+      <c r="Y85" s="28"/>
+      <c r="Z85" s="23"/>
+    </row>
+    <row r="86" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="17"/>
       <c r="B86" s="18"/>
       <c r="C86" s="34"/>
@@ -6259,12 +6065,11 @@
       <c r="U86" s="18"/>
       <c r="V86" s="18"/>
       <c r="W86" s="18"/>
-      <c r="X86" s="18"/>
-      <c r="Y86" s="25"/>
-      <c r="Z86" s="28"/>
-      <c r="AA86" s="23"/>
-    </row>
-    <row r="87" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X86" s="25"/>
+      <c r="Y86" s="28"/>
+      <c r="Z86" s="23"/>
+    </row>
+    <row r="87" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="17"/>
       <c r="B87" s="18"/>
       <c r="C87" s="34"/>
@@ -6288,12 +6093,11 @@
       <c r="U87" s="18"/>
       <c r="V87" s="18"/>
       <c r="W87" s="18"/>
-      <c r="X87" s="18"/>
-      <c r="Y87" s="25"/>
-      <c r="Z87" s="28"/>
-      <c r="AA87" s="23"/>
-    </row>
-    <row r="88" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X87" s="25"/>
+      <c r="Y87" s="28"/>
+      <c r="Z87" s="23"/>
+    </row>
+    <row r="88" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="17"/>
       <c r="B88" s="18"/>
       <c r="C88" s="34"/>
@@ -6317,12 +6121,11 @@
       <c r="U88" s="18"/>
       <c r="V88" s="18"/>
       <c r="W88" s="18"/>
-      <c r="X88" s="18"/>
-      <c r="Y88" s="25"/>
-      <c r="Z88" s="28"/>
-      <c r="AA88" s="23"/>
-    </row>
-    <row r="89" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X88" s="25"/>
+      <c r="Y88" s="28"/>
+      <c r="Z88" s="23"/>
+    </row>
+    <row r="89" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="17"/>
       <c r="B89" s="18"/>
       <c r="C89" s="34"/>
@@ -6346,12 +6149,11 @@
       <c r="U89" s="18"/>
       <c r="V89" s="18"/>
       <c r="W89" s="18"/>
-      <c r="X89" s="18"/>
-      <c r="Y89" s="25"/>
-      <c r="Z89" s="28"/>
-      <c r="AA89" s="23"/>
-    </row>
-    <row r="90" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X89" s="25"/>
+      <c r="Y89" s="28"/>
+      <c r="Z89" s="23"/>
+    </row>
+    <row r="90" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="17"/>
       <c r="B90" s="18"/>
       <c r="C90" s="34"/>
@@ -6375,12 +6177,11 @@
       <c r="U90" s="18"/>
       <c r="V90" s="18"/>
       <c r="W90" s="18"/>
-      <c r="X90" s="18"/>
-      <c r="Y90" s="25"/>
-      <c r="Z90" s="28"/>
-      <c r="AA90" s="23"/>
-    </row>
-    <row r="91" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X90" s="25"/>
+      <c r="Y90" s="28"/>
+      <c r="Z90" s="23"/>
+    </row>
+    <row r="91" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="17"/>
       <c r="B91" s="18"/>
       <c r="C91" s="34"/>
@@ -6404,12 +6205,11 @@
       <c r="U91" s="18"/>
       <c r="V91" s="18"/>
       <c r="W91" s="18"/>
-      <c r="X91" s="18"/>
-      <c r="Y91" s="25"/>
-      <c r="Z91" s="28"/>
-      <c r="AA91" s="23"/>
-    </row>
-    <row r="92" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X91" s="25"/>
+      <c r="Y91" s="28"/>
+      <c r="Z91" s="23"/>
+    </row>
+    <row r="92" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="17"/>
       <c r="B92" s="18"/>
       <c r="C92" s="34"/>
@@ -6433,12 +6233,11 @@
       <c r="U92" s="18"/>
       <c r="V92" s="18"/>
       <c r="W92" s="18"/>
-      <c r="X92" s="18"/>
-      <c r="Y92" s="25"/>
-      <c r="Z92" s="28"/>
-      <c r="AA92" s="23"/>
-    </row>
-    <row r="93" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X92" s="25"/>
+      <c r="Y92" s="28"/>
+      <c r="Z92" s="23"/>
+    </row>
+    <row r="93" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="17"/>
       <c r="B93" s="18"/>
       <c r="C93" s="34"/>
@@ -6462,12 +6261,11 @@
       <c r="U93" s="18"/>
       <c r="V93" s="18"/>
       <c r="W93" s="18"/>
-      <c r="X93" s="18"/>
-      <c r="Y93" s="25"/>
-      <c r="Z93" s="28"/>
-      <c r="AA93" s="23"/>
-    </row>
-    <row r="94" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X93" s="25"/>
+      <c r="Y93" s="28"/>
+      <c r="Z93" s="23"/>
+    </row>
+    <row r="94" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="17"/>
       <c r="B94" s="18"/>
       <c r="C94" s="34"/>
@@ -6491,12 +6289,11 @@
       <c r="U94" s="18"/>
       <c r="V94" s="18"/>
       <c r="W94" s="18"/>
-      <c r="X94" s="18"/>
-      <c r="Y94" s="25"/>
-      <c r="Z94" s="28"/>
-      <c r="AA94" s="23"/>
-    </row>
-    <row r="95" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X94" s="25"/>
+      <c r="Y94" s="28"/>
+      <c r="Z94" s="23"/>
+    </row>
+    <row r="95" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="17"/>
       <c r="B95" s="18"/>
       <c r="C95" s="34"/>
@@ -6520,12 +6317,11 @@
       <c r="U95" s="18"/>
       <c r="V95" s="18"/>
       <c r="W95" s="18"/>
-      <c r="X95" s="18"/>
-      <c r="Y95" s="25"/>
-      <c r="Z95" s="28"/>
-      <c r="AA95" s="23"/>
-    </row>
-    <row r="96" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X95" s="25"/>
+      <c r="Y95" s="28"/>
+      <c r="Z95" s="23"/>
+    </row>
+    <row r="96" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="17"/>
       <c r="B96" s="18"/>
       <c r="C96" s="34"/>
@@ -6549,12 +6345,11 @@
       <c r="U96" s="18"/>
       <c r="V96" s="18"/>
       <c r="W96" s="18"/>
-      <c r="X96" s="18"/>
-      <c r="Y96" s="25"/>
-      <c r="Z96" s="28"/>
-      <c r="AA96" s="23"/>
-    </row>
-    <row r="97" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X96" s="25"/>
+      <c r="Y96" s="28"/>
+      <c r="Z96" s="23"/>
+    </row>
+    <row r="97" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="17"/>
       <c r="B97" s="18"/>
       <c r="C97" s="34"/>
@@ -6578,12 +6373,11 @@
       <c r="U97" s="18"/>
       <c r="V97" s="18"/>
       <c r="W97" s="18"/>
-      <c r="X97" s="18"/>
-      <c r="Y97" s="25"/>
-      <c r="Z97" s="28"/>
-      <c r="AA97" s="23"/>
-    </row>
-    <row r="98" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X97" s="25"/>
+      <c r="Y97" s="28"/>
+      <c r="Z97" s="23"/>
+    </row>
+    <row r="98" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="17"/>
       <c r="B98" s="18"/>
       <c r="C98" s="34"/>
@@ -6607,12 +6401,11 @@
       <c r="U98" s="18"/>
       <c r="V98" s="18"/>
       <c r="W98" s="18"/>
-      <c r="X98" s="18"/>
-      <c r="Y98" s="25"/>
-      <c r="Z98" s="28"/>
-      <c r="AA98" s="23"/>
-    </row>
-    <row r="99" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X98" s="25"/>
+      <c r="Y98" s="28"/>
+      <c r="Z98" s="23"/>
+    </row>
+    <row r="99" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="17"/>
       <c r="B99" s="18"/>
       <c r="C99" s="34"/>
@@ -6636,12 +6429,11 @@
       <c r="U99" s="18"/>
       <c r="V99" s="18"/>
       <c r="W99" s="18"/>
-      <c r="X99" s="18"/>
-      <c r="Y99" s="25"/>
-      <c r="Z99" s="28"/>
-      <c r="AA99" s="23"/>
-    </row>
-    <row r="100" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X99" s="25"/>
+      <c r="Y99" s="28"/>
+      <c r="Z99" s="23"/>
+    </row>
+    <row r="100" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="17"/>
       <c r="B100" s="18"/>
       <c r="C100" s="34"/>
@@ -6665,12 +6457,11 @@
       <c r="U100" s="18"/>
       <c r="V100" s="18"/>
       <c r="W100" s="18"/>
-      <c r="X100" s="18"/>
-      <c r="Y100" s="25"/>
-      <c r="Z100" s="28"/>
-      <c r="AA100" s="23"/>
-    </row>
-    <row r="101" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X100" s="25"/>
+      <c r="Y100" s="28"/>
+      <c r="Z100" s="23"/>
+    </row>
+    <row r="101" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="17"/>
       <c r="B101" s="18"/>
       <c r="C101" s="34"/>
@@ -6694,12 +6485,11 @@
       <c r="U101" s="18"/>
       <c r="V101" s="18"/>
       <c r="W101" s="18"/>
-      <c r="X101" s="18"/>
-      <c r="Y101" s="25"/>
-      <c r="Z101" s="28"/>
-      <c r="AA101" s="23"/>
-    </row>
-    <row r="102" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X101" s="25"/>
+      <c r="Y101" s="28"/>
+      <c r="Z101" s="23"/>
+    </row>
+    <row r="102" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="17"/>
       <c r="B102" s="18"/>
       <c r="C102" s="34"/>
@@ -6723,12 +6513,11 @@
       <c r="U102" s="18"/>
       <c r="V102" s="18"/>
       <c r="W102" s="18"/>
-      <c r="X102" s="18"/>
-      <c r="Y102" s="25"/>
-      <c r="Z102" s="28"/>
-      <c r="AA102" s="23"/>
-    </row>
-    <row r="103" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X102" s="25"/>
+      <c r="Y102" s="28"/>
+      <c r="Z102" s="23"/>
+    </row>
+    <row r="103" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="17"/>
       <c r="B103" s="18"/>
       <c r="C103" s="34"/>
@@ -6752,12 +6541,11 @@
       <c r="U103" s="18"/>
       <c r="V103" s="18"/>
       <c r="W103" s="18"/>
-      <c r="X103" s="18"/>
-      <c r="Y103" s="25"/>
-      <c r="Z103" s="28"/>
-      <c r="AA103" s="23"/>
-    </row>
-    <row r="104" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X103" s="25"/>
+      <c r="Y103" s="28"/>
+      <c r="Z103" s="23"/>
+    </row>
+    <row r="104" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="17"/>
       <c r="B104" s="18"/>
       <c r="C104" s="34"/>
@@ -6781,12 +6569,11 @@
       <c r="U104" s="18"/>
       <c r="V104" s="18"/>
       <c r="W104" s="18"/>
-      <c r="X104" s="18"/>
-      <c r="Y104" s="25"/>
-      <c r="Z104" s="28"/>
-      <c r="AA104" s="23"/>
-    </row>
-    <row r="105" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X104" s="25"/>
+      <c r="Y104" s="28"/>
+      <c r="Z104" s="23"/>
+    </row>
+    <row r="105" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="17"/>
       <c r="B105" s="18"/>
       <c r="C105" s="34"/>
@@ -6810,12 +6597,11 @@
       <c r="U105" s="18"/>
       <c r="V105" s="18"/>
       <c r="W105" s="18"/>
-      <c r="X105" s="18"/>
-      <c r="Y105" s="25"/>
-      <c r="Z105" s="28"/>
-      <c r="AA105" s="23"/>
-    </row>
-    <row r="106" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X105" s="25"/>
+      <c r="Y105" s="28"/>
+      <c r="Z105" s="23"/>
+    </row>
+    <row r="106" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="17"/>
       <c r="B106" s="18"/>
       <c r="C106" s="34"/>
@@ -6839,12 +6625,11 @@
       <c r="U106" s="18"/>
       <c r="V106" s="18"/>
       <c r="W106" s="18"/>
-      <c r="X106" s="18"/>
-      <c r="Y106" s="25"/>
-      <c r="Z106" s="28"/>
-      <c r="AA106" s="23"/>
-    </row>
-    <row r="107" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X106" s="25"/>
+      <c r="Y106" s="28"/>
+      <c r="Z106" s="23"/>
+    </row>
+    <row r="107" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="17"/>
       <c r="B107" s="18"/>
       <c r="C107" s="34"/>
@@ -6868,12 +6653,11 @@
       <c r="U107" s="18"/>
       <c r="V107" s="18"/>
       <c r="W107" s="18"/>
-      <c r="X107" s="18"/>
-      <c r="Y107" s="25"/>
-      <c r="Z107" s="28"/>
-      <c r="AA107" s="23"/>
-    </row>
-    <row r="108" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X107" s="25"/>
+      <c r="Y107" s="28"/>
+      <c r="Z107" s="23"/>
+    </row>
+    <row r="108" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="17"/>
       <c r="B108" s="18"/>
       <c r="C108" s="34"/>
@@ -6897,12 +6681,11 @@
       <c r="U108" s="18"/>
       <c r="V108" s="18"/>
       <c r="W108" s="18"/>
-      <c r="X108" s="18"/>
-      <c r="Y108" s="25"/>
-      <c r="Z108" s="28"/>
-      <c r="AA108" s="23"/>
-    </row>
-    <row r="109" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X108" s="25"/>
+      <c r="Y108" s="28"/>
+      <c r="Z108" s="23"/>
+    </row>
+    <row r="109" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="17"/>
       <c r="B109" s="18"/>
       <c r="C109" s="34"/>
@@ -6926,12 +6709,11 @@
       <c r="U109" s="18"/>
       <c r="V109" s="18"/>
       <c r="W109" s="18"/>
-      <c r="X109" s="18"/>
-      <c r="Y109" s="25"/>
-      <c r="Z109" s="28"/>
-      <c r="AA109" s="23"/>
-    </row>
-    <row r="110" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X109" s="25"/>
+      <c r="Y109" s="28"/>
+      <c r="Z109" s="23"/>
+    </row>
+    <row r="110" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="17"/>
       <c r="B110" s="18"/>
       <c r="C110" s="34"/>
@@ -6955,12 +6737,11 @@
       <c r="U110" s="18"/>
       <c r="V110" s="18"/>
       <c r="W110" s="18"/>
-      <c r="X110" s="18"/>
-      <c r="Y110" s="25"/>
-      <c r="Z110" s="28"/>
-      <c r="AA110" s="23"/>
-    </row>
-    <row r="111" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X110" s="25"/>
+      <c r="Y110" s="28"/>
+      <c r="Z110" s="23"/>
+    </row>
+    <row r="111" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="17"/>
       <c r="B111" s="18"/>
       <c r="C111" s="34"/>
@@ -6984,12 +6765,11 @@
       <c r="U111" s="18"/>
       <c r="V111" s="18"/>
       <c r="W111" s="18"/>
-      <c r="X111" s="18"/>
-      <c r="Y111" s="25"/>
-      <c r="Z111" s="28"/>
-      <c r="AA111" s="23"/>
-    </row>
-    <row r="112" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X111" s="25"/>
+      <c r="Y111" s="28"/>
+      <c r="Z111" s="23"/>
+    </row>
+    <row r="112" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="17"/>
       <c r="B112" s="18"/>
       <c r="C112" s="34"/>
@@ -7013,12 +6793,11 @@
       <c r="U112" s="18"/>
       <c r="V112" s="18"/>
       <c r="W112" s="18"/>
-      <c r="X112" s="18"/>
-      <c r="Y112" s="25"/>
-      <c r="Z112" s="28"/>
-      <c r="AA112" s="23"/>
-    </row>
-    <row r="113" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X112" s="25"/>
+      <c r="Y112" s="28"/>
+      <c r="Z112" s="23"/>
+    </row>
+    <row r="113" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="17"/>
       <c r="B113" s="18"/>
       <c r="C113" s="34"/>
@@ -7042,12 +6821,11 @@
       <c r="U113" s="18"/>
       <c r="V113" s="18"/>
       <c r="W113" s="18"/>
-      <c r="X113" s="18"/>
-      <c r="Y113" s="25"/>
-      <c r="Z113" s="28"/>
-      <c r="AA113" s="23"/>
-    </row>
-    <row r="114" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X113" s="25"/>
+      <c r="Y113" s="28"/>
+      <c r="Z113" s="23"/>
+    </row>
+    <row r="114" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="17"/>
       <c r="B114" s="18"/>
       <c r="C114" s="34"/>
@@ -7071,12 +6849,11 @@
       <c r="U114" s="18"/>
       <c r="V114" s="18"/>
       <c r="W114" s="18"/>
-      <c r="X114" s="18"/>
-      <c r="Y114" s="25"/>
-      <c r="Z114" s="28"/>
-      <c r="AA114" s="23"/>
-    </row>
-    <row r="115" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X114" s="25"/>
+      <c r="Y114" s="28"/>
+      <c r="Z114" s="23"/>
+    </row>
+    <row r="115" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="17"/>
       <c r="B115" s="18"/>
       <c r="C115" s="34"/>
@@ -7100,12 +6877,11 @@
       <c r="U115" s="18"/>
       <c r="V115" s="18"/>
       <c r="W115" s="18"/>
-      <c r="X115" s="18"/>
-      <c r="Y115" s="25"/>
-      <c r="Z115" s="28"/>
-      <c r="AA115" s="23"/>
-    </row>
-    <row r="116" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X115" s="25"/>
+      <c r="Y115" s="28"/>
+      <c r="Z115" s="23"/>
+    </row>
+    <row r="116" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="17"/>
       <c r="B116" s="18"/>
       <c r="C116" s="34"/>
@@ -7129,12 +6905,11 @@
       <c r="U116" s="18"/>
       <c r="V116" s="18"/>
       <c r="W116" s="18"/>
-      <c r="X116" s="18"/>
-      <c r="Y116" s="25"/>
-      <c r="Z116" s="28"/>
-      <c r="AA116" s="23"/>
-    </row>
-    <row r="117" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X116" s="25"/>
+      <c r="Y116" s="28"/>
+      <c r="Z116" s="23"/>
+    </row>
+    <row r="117" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="17"/>
       <c r="B117" s="18"/>
       <c r="C117" s="34"/>
@@ -7158,12 +6933,11 @@
       <c r="U117" s="18"/>
       <c r="V117" s="18"/>
       <c r="W117" s="18"/>
-      <c r="X117" s="18"/>
-      <c r="Y117" s="25"/>
-      <c r="Z117" s="28"/>
-      <c r="AA117" s="23"/>
-    </row>
-    <row r="118" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X117" s="25"/>
+      <c r="Y117" s="28"/>
+      <c r="Z117" s="23"/>
+    </row>
+    <row r="118" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="17"/>
       <c r="B118" s="18"/>
       <c r="C118" s="34"/>
@@ -7187,12 +6961,11 @@
       <c r="U118" s="18"/>
       <c r="V118" s="18"/>
       <c r="W118" s="18"/>
-      <c r="X118" s="18"/>
-      <c r="Y118" s="25"/>
-      <c r="Z118" s="28"/>
-      <c r="AA118" s="23"/>
-    </row>
-    <row r="119" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X118" s="25"/>
+      <c r="Y118" s="28"/>
+      <c r="Z118" s="23"/>
+    </row>
+    <row r="119" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="17"/>
       <c r="B119" s="18"/>
       <c r="C119" s="34"/>
@@ -7216,12 +6989,11 @@
       <c r="U119" s="18"/>
       <c r="V119" s="18"/>
       <c r="W119" s="18"/>
-      <c r="X119" s="18"/>
-      <c r="Y119" s="25"/>
-      <c r="Z119" s="28"/>
-      <c r="AA119" s="23"/>
-    </row>
-    <row r="120" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X119" s="25"/>
+      <c r="Y119" s="28"/>
+      <c r="Z119" s="23"/>
+    </row>
+    <row r="120" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="17"/>
       <c r="B120" s="18"/>
       <c r="C120" s="34"/>
@@ -7245,12 +7017,11 @@
       <c r="U120" s="18"/>
       <c r="V120" s="18"/>
       <c r="W120" s="18"/>
-      <c r="X120" s="18"/>
-      <c r="Y120" s="25"/>
-      <c r="Z120" s="28"/>
-      <c r="AA120" s="23"/>
-    </row>
-    <row r="121" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X120" s="25"/>
+      <c r="Y120" s="28"/>
+      <c r="Z120" s="23"/>
+    </row>
+    <row r="121" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="17"/>
       <c r="B121" s="18"/>
       <c r="C121" s="34"/>
@@ -7274,12 +7045,11 @@
       <c r="U121" s="18"/>
       <c r="V121" s="18"/>
       <c r="W121" s="18"/>
-      <c r="X121" s="18"/>
-      <c r="Y121" s="25"/>
-      <c r="Z121" s="28"/>
-      <c r="AA121" s="23"/>
-    </row>
-    <row r="122" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X121" s="25"/>
+      <c r="Y121" s="28"/>
+      <c r="Z121" s="23"/>
+    </row>
+    <row r="122" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="17"/>
       <c r="B122" s="18"/>
       <c r="C122" s="34"/>
@@ -7303,12 +7073,11 @@
       <c r="U122" s="18"/>
       <c r="V122" s="18"/>
       <c r="W122" s="18"/>
-      <c r="X122" s="18"/>
-      <c r="Y122" s="25"/>
-      <c r="Z122" s="28"/>
-      <c r="AA122" s="23"/>
-    </row>
-    <row r="123" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X122" s="25"/>
+      <c r="Y122" s="28"/>
+      <c r="Z122" s="23"/>
+    </row>
+    <row r="123" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="17"/>
       <c r="B123" s="18"/>
       <c r="C123" s="34"/>
@@ -7332,12 +7101,11 @@
       <c r="U123" s="18"/>
       <c r="V123" s="18"/>
       <c r="W123" s="18"/>
-      <c r="X123" s="18"/>
-      <c r="Y123" s="25"/>
-      <c r="Z123" s="28"/>
-      <c r="AA123" s="23"/>
-    </row>
-    <row r="124" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X123" s="25"/>
+      <c r="Y123" s="28"/>
+      <c r="Z123" s="23"/>
+    </row>
+    <row r="124" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="17"/>
       <c r="B124" s="18"/>
       <c r="C124" s="34"/>
@@ -7361,12 +7129,11 @@
       <c r="U124" s="18"/>
       <c r="V124" s="18"/>
       <c r="W124" s="18"/>
-      <c r="X124" s="18"/>
-      <c r="Y124" s="25"/>
-      <c r="Z124" s="28"/>
-      <c r="AA124" s="23"/>
-    </row>
-    <row r="125" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X124" s="25"/>
+      <c r="Y124" s="28"/>
+      <c r="Z124" s="23"/>
+    </row>
+    <row r="125" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="17"/>
       <c r="B125" s="18"/>
       <c r="C125" s="34"/>
@@ -7390,12 +7157,11 @@
       <c r="U125" s="18"/>
       <c r="V125" s="18"/>
       <c r="W125" s="18"/>
-      <c r="X125" s="18"/>
-      <c r="Y125" s="25"/>
-      <c r="Z125" s="28"/>
-      <c r="AA125" s="23"/>
-    </row>
-    <row r="126" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X125" s="25"/>
+      <c r="Y125" s="28"/>
+      <c r="Z125" s="23"/>
+    </row>
+    <row r="126" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="17"/>
       <c r="B126" s="18"/>
       <c r="C126" s="34"/>
@@ -7419,12 +7185,11 @@
       <c r="U126" s="18"/>
       <c r="V126" s="18"/>
       <c r="W126" s="18"/>
-      <c r="X126" s="18"/>
-      <c r="Y126" s="25"/>
-      <c r="Z126" s="28"/>
-      <c r="AA126" s="23"/>
-    </row>
-    <row r="127" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X126" s="25"/>
+      <c r="Y126" s="28"/>
+      <c r="Z126" s="23"/>
+    </row>
+    <row r="127" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="17"/>
       <c r="B127" s="18"/>
       <c r="C127" s="34"/>
@@ -7448,12 +7213,11 @@
       <c r="U127" s="18"/>
       <c r="V127" s="18"/>
       <c r="W127" s="18"/>
-      <c r="X127" s="18"/>
-      <c r="Y127" s="25"/>
-      <c r="Z127" s="28"/>
-      <c r="AA127" s="23"/>
-    </row>
-    <row r="128" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X127" s="25"/>
+      <c r="Y127" s="28"/>
+      <c r="Z127" s="23"/>
+    </row>
+    <row r="128" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="17"/>
       <c r="B128" s="18"/>
       <c r="C128" s="34"/>
@@ -7477,12 +7241,11 @@
       <c r="U128" s="18"/>
       <c r="V128" s="18"/>
       <c r="W128" s="18"/>
-      <c r="X128" s="18"/>
-      <c r="Y128" s="25"/>
-      <c r="Z128" s="28"/>
-      <c r="AA128" s="23"/>
-    </row>
-    <row r="129" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X128" s="25"/>
+      <c r="Y128" s="28"/>
+      <c r="Z128" s="23"/>
+    </row>
+    <row r="129" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="17"/>
       <c r="B129" s="18"/>
       <c r="C129" s="34"/>
@@ -7506,12 +7269,11 @@
       <c r="U129" s="18"/>
       <c r="V129" s="18"/>
       <c r="W129" s="18"/>
-      <c r="X129" s="18"/>
-      <c r="Y129" s="25"/>
-      <c r="Z129" s="28"/>
-      <c r="AA129" s="23"/>
-    </row>
-    <row r="130" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X129" s="25"/>
+      <c r="Y129" s="28"/>
+      <c r="Z129" s="23"/>
+    </row>
+    <row r="130" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="17"/>
       <c r="B130" s="18"/>
       <c r="C130" s="34"/>
@@ -7535,12 +7297,11 @@
       <c r="U130" s="18"/>
       <c r="V130" s="18"/>
       <c r="W130" s="18"/>
-      <c r="X130" s="18"/>
-      <c r="Y130" s="25"/>
-      <c r="Z130" s="28"/>
-      <c r="AA130" s="23"/>
-    </row>
-    <row r="131" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X130" s="25"/>
+      <c r="Y130" s="28"/>
+      <c r="Z130" s="23"/>
+    </row>
+    <row r="131" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="17"/>
       <c r="B131" s="18"/>
       <c r="C131" s="34"/>
@@ -7564,12 +7325,11 @@
       <c r="U131" s="18"/>
       <c r="V131" s="18"/>
       <c r="W131" s="18"/>
-      <c r="X131" s="18"/>
-      <c r="Y131" s="25"/>
-      <c r="Z131" s="28"/>
-      <c r="AA131" s="23"/>
-    </row>
-    <row r="132" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X131" s="25"/>
+      <c r="Y131" s="28"/>
+      <c r="Z131" s="23"/>
+    </row>
+    <row r="132" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="17"/>
       <c r="B132" s="18"/>
       <c r="C132" s="34"/>
@@ -7593,12 +7353,11 @@
       <c r="U132" s="18"/>
       <c r="V132" s="18"/>
       <c r="W132" s="18"/>
-      <c r="X132" s="18"/>
-      <c r="Y132" s="25"/>
-      <c r="Z132" s="28"/>
-      <c r="AA132" s="23"/>
-    </row>
-    <row r="133" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X132" s="25"/>
+      <c r="Y132" s="28"/>
+      <c r="Z132" s="23"/>
+    </row>
+    <row r="133" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="17"/>
       <c r="B133" s="18"/>
       <c r="C133" s="34"/>
@@ -7622,12 +7381,11 @@
       <c r="U133" s="18"/>
       <c r="V133" s="18"/>
       <c r="W133" s="18"/>
-      <c r="X133" s="18"/>
-      <c r="Y133" s="25"/>
-      <c r="Z133" s="28"/>
-      <c r="AA133" s="23"/>
-    </row>
-    <row r="134" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X133" s="25"/>
+      <c r="Y133" s="28"/>
+      <c r="Z133" s="23"/>
+    </row>
+    <row r="134" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="17"/>
       <c r="B134" s="18"/>
       <c r="C134" s="34"/>
@@ -7651,12 +7409,11 @@
       <c r="U134" s="18"/>
       <c r="V134" s="18"/>
       <c r="W134" s="18"/>
-      <c r="X134" s="18"/>
-      <c r="Y134" s="25"/>
-      <c r="Z134" s="28"/>
-      <c r="AA134" s="23"/>
-    </row>
-    <row r="135" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X134" s="25"/>
+      <c r="Y134" s="28"/>
+      <c r="Z134" s="23"/>
+    </row>
+    <row r="135" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="17"/>
       <c r="B135" s="18"/>
       <c r="C135" s="34"/>
@@ -7680,12 +7437,11 @@
       <c r="U135" s="18"/>
       <c r="V135" s="18"/>
       <c r="W135" s="18"/>
-      <c r="X135" s="18"/>
-      <c r="Y135" s="25"/>
-      <c r="Z135" s="28"/>
-      <c r="AA135" s="23"/>
-    </row>
-    <row r="136" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X135" s="25"/>
+      <c r="Y135" s="28"/>
+      <c r="Z135" s="23"/>
+    </row>
+    <row r="136" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="17"/>
       <c r="B136" s="18"/>
       <c r="C136" s="34"/>
@@ -7709,12 +7465,11 @@
       <c r="U136" s="18"/>
       <c r="V136" s="18"/>
       <c r="W136" s="18"/>
-      <c r="X136" s="18"/>
-      <c r="Y136" s="25"/>
-      <c r="Z136" s="28"/>
-      <c r="AA136" s="23"/>
-    </row>
-    <row r="137" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X136" s="25"/>
+      <c r="Y136" s="28"/>
+      <c r="Z136" s="23"/>
+    </row>
+    <row r="137" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="17"/>
       <c r="B137" s="18"/>
       <c r="C137" s="34"/>
@@ -7738,12 +7493,11 @@
       <c r="U137" s="18"/>
       <c r="V137" s="18"/>
       <c r="W137" s="18"/>
-      <c r="X137" s="18"/>
-      <c r="Y137" s="25"/>
-      <c r="Z137" s="28"/>
-      <c r="AA137" s="23"/>
-    </row>
-    <row r="138" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X137" s="25"/>
+      <c r="Y137" s="28"/>
+      <c r="Z137" s="23"/>
+    </row>
+    <row r="138" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="17"/>
       <c r="B138" s="18"/>
       <c r="C138" s="34"/>
@@ -7767,12 +7521,11 @@
       <c r="U138" s="18"/>
       <c r="V138" s="18"/>
       <c r="W138" s="18"/>
-      <c r="X138" s="18"/>
-      <c r="Y138" s="25"/>
-      <c r="Z138" s="28"/>
-      <c r="AA138" s="23"/>
-    </row>
-    <row r="139" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X138" s="25"/>
+      <c r="Y138" s="28"/>
+      <c r="Z138" s="23"/>
+    </row>
+    <row r="139" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="17"/>
       <c r="B139" s="18"/>
       <c r="C139" s="34"/>
@@ -7796,12 +7549,11 @@
       <c r="U139" s="18"/>
       <c r="V139" s="18"/>
       <c r="W139" s="18"/>
-      <c r="X139" s="18"/>
-      <c r="Y139" s="25"/>
-      <c r="Z139" s="28"/>
-      <c r="AA139" s="23"/>
-    </row>
-    <row r="140" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X139" s="25"/>
+      <c r="Y139" s="28"/>
+      <c r="Z139" s="23"/>
+    </row>
+    <row r="140" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="17"/>
       <c r="B140" s="18"/>
       <c r="C140" s="34"/>
@@ -7825,12 +7577,11 @@
       <c r="U140" s="18"/>
       <c r="V140" s="18"/>
       <c r="W140" s="18"/>
-      <c r="X140" s="18"/>
-      <c r="Y140" s="25"/>
-      <c r="Z140" s="28"/>
-      <c r="AA140" s="23"/>
-    </row>
-    <row r="141" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X140" s="25"/>
+      <c r="Y140" s="28"/>
+      <c r="Z140" s="23"/>
+    </row>
+    <row r="141" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="17"/>
       <c r="B141" s="18"/>
       <c r="C141" s="34"/>
@@ -7854,12 +7605,11 @@
       <c r="U141" s="18"/>
       <c r="V141" s="18"/>
       <c r="W141" s="18"/>
-      <c r="X141" s="18"/>
-      <c r="Y141" s="25"/>
-      <c r="Z141" s="28"/>
-      <c r="AA141" s="23"/>
-    </row>
-    <row r="142" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X141" s="25"/>
+      <c r="Y141" s="28"/>
+      <c r="Z141" s="23"/>
+    </row>
+    <row r="142" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="17"/>
       <c r="B142" s="18"/>
       <c r="C142" s="34"/>
@@ -7883,12 +7633,11 @@
       <c r="U142" s="18"/>
       <c r="V142" s="18"/>
       <c r="W142" s="18"/>
-      <c r="X142" s="18"/>
-      <c r="Y142" s="25"/>
-      <c r="Z142" s="28"/>
-      <c r="AA142" s="23"/>
-    </row>
-    <row r="143" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X142" s="25"/>
+      <c r="Y142" s="28"/>
+      <c r="Z142" s="23"/>
+    </row>
+    <row r="143" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="17"/>
       <c r="B143" s="18"/>
       <c r="C143" s="34"/>
@@ -7912,12 +7661,11 @@
       <c r="U143" s="18"/>
       <c r="V143" s="18"/>
       <c r="W143" s="18"/>
-      <c r="X143" s="18"/>
-      <c r="Y143" s="25"/>
-      <c r="Z143" s="28"/>
-      <c r="AA143" s="23"/>
-    </row>
-    <row r="144" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X143" s="25"/>
+      <c r="Y143" s="28"/>
+      <c r="Z143" s="23"/>
+    </row>
+    <row r="144" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="17"/>
       <c r="B144" s="18"/>
       <c r="C144" s="34"/>
@@ -7941,12 +7689,11 @@
       <c r="U144" s="18"/>
       <c r="V144" s="18"/>
       <c r="W144" s="18"/>
-      <c r="X144" s="18"/>
-      <c r="Y144" s="25"/>
-      <c r="Z144" s="28"/>
-      <c r="AA144" s="23"/>
-    </row>
-    <row r="145" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X144" s="25"/>
+      <c r="Y144" s="28"/>
+      <c r="Z144" s="23"/>
+    </row>
+    <row r="145" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="17"/>
       <c r="B145" s="18"/>
       <c r="C145" s="34"/>
@@ -7970,12 +7717,11 @@
       <c r="U145" s="18"/>
       <c r="V145" s="18"/>
       <c r="W145" s="18"/>
-      <c r="X145" s="18"/>
-      <c r="Y145" s="25"/>
-      <c r="Z145" s="28"/>
-      <c r="AA145" s="23"/>
-    </row>
-    <row r="146" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X145" s="25"/>
+      <c r="Y145" s="28"/>
+      <c r="Z145" s="23"/>
+    </row>
+    <row r="146" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="17"/>
       <c r="B146" s="18"/>
       <c r="C146" s="34"/>
@@ -7999,12 +7745,11 @@
       <c r="U146" s="18"/>
       <c r="V146" s="18"/>
       <c r="W146" s="18"/>
-      <c r="X146" s="18"/>
-      <c r="Y146" s="25"/>
-      <c r="Z146" s="28"/>
-      <c r="AA146" s="23"/>
-    </row>
-    <row r="147" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X146" s="25"/>
+      <c r="Y146" s="28"/>
+      <c r="Z146" s="23"/>
+    </row>
+    <row r="147" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="17"/>
       <c r="B147" s="18"/>
       <c r="C147" s="34"/>
@@ -8028,12 +7773,11 @@
       <c r="U147" s="18"/>
       <c r="V147" s="18"/>
       <c r="W147" s="18"/>
-      <c r="X147" s="18"/>
-      <c r="Y147" s="25"/>
-      <c r="Z147" s="28"/>
-      <c r="AA147" s="23"/>
-    </row>
-    <row r="148" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X147" s="25"/>
+      <c r="Y147" s="28"/>
+      <c r="Z147" s="23"/>
+    </row>
+    <row r="148" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="17"/>
       <c r="B148" s="18"/>
       <c r="C148" s="34"/>
@@ -8057,12 +7801,11 @@
       <c r="U148" s="18"/>
       <c r="V148" s="18"/>
       <c r="W148" s="18"/>
-      <c r="X148" s="18"/>
-      <c r="Y148" s="25"/>
-      <c r="Z148" s="28"/>
-      <c r="AA148" s="23"/>
-    </row>
-    <row r="149" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X148" s="25"/>
+      <c r="Y148" s="28"/>
+      <c r="Z148" s="23"/>
+    </row>
+    <row r="149" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="17"/>
       <c r="B149" s="18"/>
       <c r="C149" s="34"/>
@@ -8086,12 +7829,11 @@
       <c r="U149" s="18"/>
       <c r="V149" s="18"/>
       <c r="W149" s="18"/>
-      <c r="X149" s="18"/>
-      <c r="Y149" s="25"/>
-      <c r="Z149" s="28"/>
-      <c r="AA149" s="23"/>
-    </row>
-    <row r="150" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X149" s="25"/>
+      <c r="Y149" s="28"/>
+      <c r="Z149" s="23"/>
+    </row>
+    <row r="150" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="17"/>
       <c r="B150" s="18"/>
       <c r="C150" s="34"/>
@@ -8115,12 +7857,11 @@
       <c r="U150" s="18"/>
       <c r="V150" s="18"/>
       <c r="W150" s="18"/>
-      <c r="X150" s="18"/>
-      <c r="Y150" s="25"/>
-      <c r="Z150" s="28"/>
-      <c r="AA150" s="23"/>
-    </row>
-    <row r="151" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X150" s="25"/>
+      <c r="Y150" s="28"/>
+      <c r="Z150" s="23"/>
+    </row>
+    <row r="151" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="17"/>
       <c r="B151" s="18"/>
       <c r="C151" s="34"/>
@@ -8144,12 +7885,11 @@
       <c r="U151" s="18"/>
       <c r="V151" s="18"/>
       <c r="W151" s="18"/>
-      <c r="X151" s="18"/>
-      <c r="Y151" s="25"/>
-      <c r="Z151" s="28"/>
-      <c r="AA151" s="23"/>
-    </row>
-    <row r="152" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X151" s="25"/>
+      <c r="Y151" s="28"/>
+      <c r="Z151" s="23"/>
+    </row>
+    <row r="152" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="17"/>
       <c r="B152" s="18"/>
       <c r="C152" s="34"/>
@@ -8173,12 +7913,11 @@
       <c r="U152" s="18"/>
       <c r="V152" s="18"/>
       <c r="W152" s="18"/>
-      <c r="X152" s="18"/>
-      <c r="Y152" s="25"/>
-      <c r="Z152" s="28"/>
-      <c r="AA152" s="23"/>
-    </row>
-    <row r="153" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X152" s="25"/>
+      <c r="Y152" s="28"/>
+      <c r="Z152" s="23"/>
+    </row>
+    <row r="153" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="17"/>
       <c r="B153" s="18"/>
       <c r="C153" s="34"/>
@@ -8202,12 +7941,11 @@
       <c r="U153" s="18"/>
       <c r="V153" s="18"/>
       <c r="W153" s="18"/>
-      <c r="X153" s="18"/>
-      <c r="Y153" s="25"/>
-      <c r="Z153" s="28"/>
-      <c r="AA153" s="23"/>
-    </row>
-    <row r="154" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X153" s="25"/>
+      <c r="Y153" s="28"/>
+      <c r="Z153" s="23"/>
+    </row>
+    <row r="154" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="17"/>
       <c r="B154" s="18"/>
       <c r="C154" s="34"/>
@@ -8231,12 +7969,11 @@
       <c r="U154" s="18"/>
       <c r="V154" s="18"/>
       <c r="W154" s="18"/>
-      <c r="X154" s="18"/>
-      <c r="Y154" s="25"/>
-      <c r="Z154" s="28"/>
-      <c r="AA154" s="23"/>
-    </row>
-    <row r="155" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X154" s="25"/>
+      <c r="Y154" s="28"/>
+      <c r="Z154" s="23"/>
+    </row>
+    <row r="155" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="17"/>
       <c r="B155" s="18"/>
       <c r="C155" s="34"/>
@@ -8260,12 +7997,11 @@
       <c r="U155" s="18"/>
       <c r="V155" s="18"/>
       <c r="W155" s="18"/>
-      <c r="X155" s="18"/>
-      <c r="Y155" s="25"/>
-      <c r="Z155" s="28"/>
-      <c r="AA155" s="23"/>
-    </row>
-    <row r="156" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X155" s="25"/>
+      <c r="Y155" s="28"/>
+      <c r="Z155" s="23"/>
+    </row>
+    <row r="156" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="17"/>
       <c r="B156" s="18"/>
       <c r="C156" s="34"/>
@@ -8289,12 +8025,11 @@
       <c r="U156" s="18"/>
       <c r="V156" s="18"/>
       <c r="W156" s="18"/>
-      <c r="X156" s="18"/>
-      <c r="Y156" s="25"/>
-      <c r="Z156" s="28"/>
-      <c r="AA156" s="23"/>
-    </row>
-    <row r="157" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X156" s="25"/>
+      <c r="Y156" s="28"/>
+      <c r="Z156" s="23"/>
+    </row>
+    <row r="157" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="17"/>
       <c r="B157" s="18"/>
       <c r="C157" s="34"/>
@@ -8318,12 +8053,11 @@
       <c r="U157" s="18"/>
       <c r="V157" s="18"/>
       <c r="W157" s="18"/>
-      <c r="X157" s="18"/>
-      <c r="Y157" s="25"/>
-      <c r="Z157" s="28"/>
-      <c r="AA157" s="23"/>
-    </row>
-    <row r="158" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X157" s="25"/>
+      <c r="Y157" s="28"/>
+      <c r="Z157" s="23"/>
+    </row>
+    <row r="158" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="17"/>
       <c r="B158" s="18"/>
       <c r="C158" s="34"/>
@@ -8347,12 +8081,11 @@
       <c r="U158" s="18"/>
       <c r="V158" s="18"/>
       <c r="W158" s="18"/>
-      <c r="X158" s="18"/>
-      <c r="Y158" s="25"/>
-      <c r="Z158" s="28"/>
-      <c r="AA158" s="23"/>
-    </row>
-    <row r="159" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X158" s="25"/>
+      <c r="Y158" s="28"/>
+      <c r="Z158" s="23"/>
+    </row>
+    <row r="159" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="17"/>
       <c r="B159" s="18"/>
       <c r="C159" s="34"/>
@@ -8376,12 +8109,11 @@
       <c r="U159" s="18"/>
       <c r="V159" s="18"/>
       <c r="W159" s="18"/>
-      <c r="X159" s="18"/>
-      <c r="Y159" s="25"/>
-      <c r="Z159" s="28"/>
-      <c r="AA159" s="23"/>
-    </row>
-    <row r="160" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X159" s="25"/>
+      <c r="Y159" s="28"/>
+      <c r="Z159" s="23"/>
+    </row>
+    <row r="160" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="17"/>
       <c r="B160" s="18"/>
       <c r="C160" s="34"/>
@@ -8405,12 +8137,11 @@
       <c r="U160" s="18"/>
       <c r="V160" s="18"/>
       <c r="W160" s="18"/>
-      <c r="X160" s="18"/>
-      <c r="Y160" s="25"/>
-      <c r="Z160" s="28"/>
-      <c r="AA160" s="23"/>
-    </row>
-    <row r="161" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X160" s="25"/>
+      <c r="Y160" s="28"/>
+      <c r="Z160" s="23"/>
+    </row>
+    <row r="161" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="17"/>
       <c r="B161" s="18"/>
       <c r="C161" s="34"/>
@@ -8434,12 +8165,11 @@
       <c r="U161" s="18"/>
       <c r="V161" s="18"/>
       <c r="W161" s="18"/>
-      <c r="X161" s="18"/>
-      <c r="Y161" s="25"/>
-      <c r="Z161" s="28"/>
-      <c r="AA161" s="23"/>
-    </row>
-    <row r="162" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X161" s="25"/>
+      <c r="Y161" s="28"/>
+      <c r="Z161" s="23"/>
+    </row>
+    <row r="162" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="17"/>
       <c r="B162" s="18"/>
       <c r="C162" s="34"/>
@@ -8463,12 +8193,11 @@
       <c r="U162" s="18"/>
       <c r="V162" s="18"/>
       <c r="W162" s="18"/>
-      <c r="X162" s="18"/>
-      <c r="Y162" s="25"/>
-      <c r="Z162" s="28"/>
-      <c r="AA162" s="23"/>
-    </row>
-    <row r="163" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X162" s="25"/>
+      <c r="Y162" s="28"/>
+      <c r="Z162" s="23"/>
+    </row>
+    <row r="163" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="17"/>
       <c r="B163" s="18"/>
       <c r="C163" s="34"/>
@@ -8492,12 +8221,11 @@
       <c r="U163" s="18"/>
       <c r="V163" s="18"/>
       <c r="W163" s="18"/>
-      <c r="X163" s="18"/>
-      <c r="Y163" s="25"/>
-      <c r="Z163" s="28"/>
-      <c r="AA163" s="23"/>
-    </row>
-    <row r="164" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X163" s="25"/>
+      <c r="Y163" s="28"/>
+      <c r="Z163" s="23"/>
+    </row>
+    <row r="164" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="17"/>
       <c r="B164" s="18"/>
       <c r="C164" s="34"/>
@@ -8521,12 +8249,11 @@
       <c r="U164" s="18"/>
       <c r="V164" s="18"/>
       <c r="W164" s="18"/>
-      <c r="X164" s="18"/>
-      <c r="Y164" s="25"/>
-      <c r="Z164" s="28"/>
-      <c r="AA164" s="23"/>
-    </row>
-    <row r="165" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X164" s="25"/>
+      <c r="Y164" s="28"/>
+      <c r="Z164" s="23"/>
+    </row>
+    <row r="165" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="17"/>
       <c r="B165" s="18"/>
       <c r="C165" s="34"/>
@@ -8550,12 +8277,11 @@
       <c r="U165" s="18"/>
       <c r="V165" s="18"/>
       <c r="W165" s="18"/>
-      <c r="X165" s="18"/>
-      <c r="Y165" s="25"/>
-      <c r="Z165" s="28"/>
-      <c r="AA165" s="23"/>
-    </row>
-    <row r="166" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X165" s="25"/>
+      <c r="Y165" s="28"/>
+      <c r="Z165" s="23"/>
+    </row>
+    <row r="166" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="17"/>
       <c r="B166" s="18"/>
       <c r="C166" s="34"/>
@@ -8579,12 +8305,11 @@
       <c r="U166" s="18"/>
       <c r="V166" s="18"/>
       <c r="W166" s="18"/>
-      <c r="X166" s="18"/>
-      <c r="Y166" s="25"/>
-      <c r="Z166" s="28"/>
-      <c r="AA166" s="23"/>
-    </row>
-    <row r="167" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X166" s="25"/>
+      <c r="Y166" s="28"/>
+      <c r="Z166" s="23"/>
+    </row>
+    <row r="167" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="17"/>
       <c r="B167" s="18"/>
       <c r="C167" s="34"/>
@@ -8608,12 +8333,11 @@
       <c r="U167" s="18"/>
       <c r="V167" s="18"/>
       <c r="W167" s="18"/>
-      <c r="X167" s="18"/>
-      <c r="Y167" s="25"/>
-      <c r="Z167" s="28"/>
-      <c r="AA167" s="23"/>
-    </row>
-    <row r="168" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X167" s="25"/>
+      <c r="Y167" s="28"/>
+      <c r="Z167" s="23"/>
+    </row>
+    <row r="168" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="17"/>
       <c r="B168" s="18"/>
       <c r="C168" s="34"/>
@@ -8637,12 +8361,11 @@
       <c r="U168" s="18"/>
       <c r="V168" s="18"/>
       <c r="W168" s="18"/>
-      <c r="X168" s="18"/>
-      <c r="Y168" s="25"/>
-      <c r="Z168" s="28"/>
-      <c r="AA168" s="23"/>
-    </row>
-    <row r="169" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X168" s="25"/>
+      <c r="Y168" s="28"/>
+      <c r="Z168" s="23"/>
+    </row>
+    <row r="169" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="17"/>
       <c r="B169" s="18"/>
       <c r="C169" s="34"/>
@@ -8666,12 +8389,11 @@
       <c r="U169" s="18"/>
       <c r="V169" s="18"/>
       <c r="W169" s="18"/>
-      <c r="X169" s="18"/>
-      <c r="Y169" s="25"/>
-      <c r="Z169" s="28"/>
-      <c r="AA169" s="23"/>
-    </row>
-    <row r="170" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X169" s="25"/>
+      <c r="Y169" s="28"/>
+      <c r="Z169" s="23"/>
+    </row>
+    <row r="170" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="17"/>
       <c r="B170" s="18"/>
       <c r="C170" s="34"/>
@@ -8695,12 +8417,11 @@
       <c r="U170" s="18"/>
       <c r="V170" s="18"/>
       <c r="W170" s="18"/>
-      <c r="X170" s="18"/>
-      <c r="Y170" s="25"/>
-      <c r="Z170" s="28"/>
-      <c r="AA170" s="23"/>
-    </row>
-    <row r="171" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X170" s="25"/>
+      <c r="Y170" s="28"/>
+      <c r="Z170" s="23"/>
+    </row>
+    <row r="171" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="17"/>
       <c r="B171" s="18"/>
       <c r="C171" s="34"/>
@@ -8724,12 +8445,11 @@
       <c r="U171" s="18"/>
       <c r="V171" s="18"/>
       <c r="W171" s="18"/>
-      <c r="X171" s="18"/>
-      <c r="Y171" s="25"/>
-      <c r="Z171" s="28"/>
-      <c r="AA171" s="23"/>
-    </row>
-    <row r="172" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X171" s="25"/>
+      <c r="Y171" s="28"/>
+      <c r="Z171" s="23"/>
+    </row>
+    <row r="172" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="17"/>
       <c r="B172" s="18"/>
       <c r="C172" s="34"/>
@@ -8753,12 +8473,11 @@
       <c r="U172" s="18"/>
       <c r="V172" s="18"/>
       <c r="W172" s="18"/>
-      <c r="X172" s="18"/>
-      <c r="Y172" s="25"/>
-      <c r="Z172" s="28"/>
-      <c r="AA172" s="23"/>
-    </row>
-    <row r="173" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X172" s="25"/>
+      <c r="Y172" s="28"/>
+      <c r="Z172" s="23"/>
+    </row>
+    <row r="173" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="17"/>
       <c r="B173" s="18"/>
       <c r="C173" s="34"/>
@@ -8782,12 +8501,11 @@
       <c r="U173" s="18"/>
       <c r="V173" s="18"/>
       <c r="W173" s="18"/>
-      <c r="X173" s="18"/>
-      <c r="Y173" s="25"/>
-      <c r="Z173" s="28"/>
-      <c r="AA173" s="23"/>
-    </row>
-    <row r="174" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X173" s="25"/>
+      <c r="Y173" s="28"/>
+      <c r="Z173" s="23"/>
+    </row>
+    <row r="174" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="17"/>
       <c r="B174" s="18"/>
       <c r="C174" s="34"/>
@@ -8811,12 +8529,11 @@
       <c r="U174" s="18"/>
       <c r="V174" s="18"/>
       <c r="W174" s="18"/>
-      <c r="X174" s="18"/>
-      <c r="Y174" s="25"/>
-      <c r="Z174" s="28"/>
-      <c r="AA174" s="23"/>
-    </row>
-    <row r="175" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X174" s="25"/>
+      <c r="Y174" s="28"/>
+      <c r="Z174" s="23"/>
+    </row>
+    <row r="175" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="17"/>
       <c r="B175" s="18"/>
       <c r="C175" s="34"/>
@@ -8840,12 +8557,11 @@
       <c r="U175" s="18"/>
       <c r="V175" s="18"/>
       <c r="W175" s="18"/>
-      <c r="X175" s="18"/>
-      <c r="Y175" s="25"/>
-      <c r="Z175" s="28"/>
-      <c r="AA175" s="23"/>
-    </row>
-    <row r="176" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X175" s="25"/>
+      <c r="Y175" s="28"/>
+      <c r="Z175" s="23"/>
+    </row>
+    <row r="176" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="17"/>
       <c r="B176" s="18"/>
       <c r="C176" s="34"/>
@@ -8869,12 +8585,11 @@
       <c r="U176" s="18"/>
       <c r="V176" s="18"/>
       <c r="W176" s="18"/>
-      <c r="X176" s="18"/>
-      <c r="Y176" s="25"/>
-      <c r="Z176" s="28"/>
-      <c r="AA176" s="23"/>
-    </row>
-    <row r="177" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X176" s="25"/>
+      <c r="Y176" s="28"/>
+      <c r="Z176" s="23"/>
+    </row>
+    <row r="177" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="17"/>
       <c r="B177" s="18"/>
       <c r="C177" s="34"/>
@@ -8898,12 +8613,11 @@
       <c r="U177" s="18"/>
       <c r="V177" s="18"/>
       <c r="W177" s="18"/>
-      <c r="X177" s="18"/>
-      <c r="Y177" s="25"/>
-      <c r="Z177" s="28"/>
-      <c r="AA177" s="23"/>
-    </row>
-    <row r="178" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X177" s="25"/>
+      <c r="Y177" s="28"/>
+      <c r="Z177" s="23"/>
+    </row>
+    <row r="178" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="17"/>
       <c r="B178" s="18"/>
       <c r="C178" s="34"/>
@@ -8927,12 +8641,11 @@
       <c r="U178" s="18"/>
       <c r="V178" s="18"/>
       <c r="W178" s="18"/>
-      <c r="X178" s="18"/>
-      <c r="Y178" s="25"/>
-      <c r="Z178" s="28"/>
-      <c r="AA178" s="23"/>
-    </row>
-    <row r="179" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X178" s="25"/>
+      <c r="Y178" s="28"/>
+      <c r="Z178" s="23"/>
+    </row>
+    <row r="179" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="17"/>
       <c r="B179" s="18"/>
       <c r="C179" s="34"/>
@@ -8956,12 +8669,11 @@
       <c r="U179" s="18"/>
       <c r="V179" s="18"/>
       <c r="W179" s="18"/>
-      <c r="X179" s="18"/>
-      <c r="Y179" s="25"/>
-      <c r="Z179" s="28"/>
-      <c r="AA179" s="23"/>
-    </row>
-    <row r="180" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X179" s="25"/>
+      <c r="Y179" s="28"/>
+      <c r="Z179" s="23"/>
+    </row>
+    <row r="180" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="17"/>
       <c r="B180" s="18"/>
       <c r="C180" s="34"/>
@@ -8985,12 +8697,11 @@
       <c r="U180" s="18"/>
       <c r="V180" s="18"/>
       <c r="W180" s="18"/>
-      <c r="X180" s="18"/>
-      <c r="Y180" s="25"/>
-      <c r="Z180" s="28"/>
-      <c r="AA180" s="23"/>
-    </row>
-    <row r="181" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X180" s="25"/>
+      <c r="Y180" s="28"/>
+      <c r="Z180" s="23"/>
+    </row>
+    <row r="181" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="17"/>
       <c r="B181" s="18"/>
       <c r="C181" s="34"/>
@@ -9014,12 +8725,11 @@
       <c r="U181" s="18"/>
       <c r="V181" s="18"/>
       <c r="W181" s="18"/>
-      <c r="X181" s="18"/>
-      <c r="Y181" s="25"/>
-      <c r="Z181" s="28"/>
-      <c r="AA181" s="23"/>
-    </row>
-    <row r="182" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X181" s="25"/>
+      <c r="Y181" s="28"/>
+      <c r="Z181" s="23"/>
+    </row>
+    <row r="182" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="17"/>
       <c r="B182" s="18"/>
       <c r="C182" s="34"/>
@@ -9043,12 +8753,11 @@
       <c r="U182" s="18"/>
       <c r="V182" s="18"/>
       <c r="W182" s="18"/>
-      <c r="X182" s="18"/>
-      <c r="Y182" s="25"/>
-      <c r="Z182" s="28"/>
-      <c r="AA182" s="23"/>
-    </row>
-    <row r="183" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X182" s="25"/>
+      <c r="Y182" s="28"/>
+      <c r="Z182" s="23"/>
+    </row>
+    <row r="183" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="17"/>
       <c r="B183" s="18"/>
       <c r="C183" s="34"/>
@@ -9072,12 +8781,11 @@
       <c r="U183" s="18"/>
       <c r="V183" s="18"/>
       <c r="W183" s="18"/>
-      <c r="X183" s="18"/>
-      <c r="Y183" s="25"/>
-      <c r="Z183" s="28"/>
-      <c r="AA183" s="23"/>
-    </row>
-    <row r="184" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X183" s="25"/>
+      <c r="Y183" s="28"/>
+      <c r="Z183" s="23"/>
+    </row>
+    <row r="184" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="17"/>
       <c r="B184" s="18"/>
       <c r="C184" s="34"/>
@@ -9101,12 +8809,11 @@
       <c r="U184" s="18"/>
       <c r="V184" s="18"/>
       <c r="W184" s="18"/>
-      <c r="X184" s="18"/>
-      <c r="Y184" s="25"/>
-      <c r="Z184" s="28"/>
-      <c r="AA184" s="23"/>
-    </row>
-    <row r="185" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X184" s="25"/>
+      <c r="Y184" s="28"/>
+      <c r="Z184" s="23"/>
+    </row>
+    <row r="185" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="17"/>
       <c r="B185" s="18"/>
       <c r="C185" s="34"/>
@@ -9130,12 +8837,11 @@
       <c r="U185" s="18"/>
       <c r="V185" s="18"/>
       <c r="W185" s="18"/>
-      <c r="X185" s="18"/>
-      <c r="Y185" s="25"/>
-      <c r="Z185" s="28"/>
-      <c r="AA185" s="23"/>
-    </row>
-    <row r="186" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X185" s="25"/>
+      <c r="Y185" s="28"/>
+      <c r="Z185" s="23"/>
+    </row>
+    <row r="186" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="17"/>
       <c r="B186" s="18"/>
       <c r="C186" s="34"/>
@@ -9159,12 +8865,11 @@
       <c r="U186" s="18"/>
       <c r="V186" s="18"/>
       <c r="W186" s="18"/>
-      <c r="X186" s="18"/>
-      <c r="Y186" s="25"/>
-      <c r="Z186" s="28"/>
-      <c r="AA186" s="23"/>
-    </row>
-    <row r="187" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X186" s="25"/>
+      <c r="Y186" s="28"/>
+      <c r="Z186" s="23"/>
+    </row>
+    <row r="187" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="17"/>
       <c r="B187" s="18"/>
       <c r="C187" s="34"/>
@@ -9188,12 +8893,11 @@
       <c r="U187" s="18"/>
       <c r="V187" s="18"/>
       <c r="W187" s="18"/>
-      <c r="X187" s="18"/>
-      <c r="Y187" s="25"/>
-      <c r="Z187" s="28"/>
-      <c r="AA187" s="23"/>
-    </row>
-    <row r="188" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X187" s="25"/>
+      <c r="Y187" s="28"/>
+      <c r="Z187" s="23"/>
+    </row>
+    <row r="188" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="17"/>
       <c r="B188" s="18"/>
       <c r="C188" s="34"/>
@@ -9217,12 +8921,11 @@
       <c r="U188" s="18"/>
       <c r="V188" s="18"/>
       <c r="W188" s="18"/>
-      <c r="X188" s="18"/>
-      <c r="Y188" s="25"/>
-      <c r="Z188" s="28"/>
-      <c r="AA188" s="23"/>
-    </row>
-    <row r="189" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X188" s="25"/>
+      <c r="Y188" s="28"/>
+      <c r="Z188" s="23"/>
+    </row>
+    <row r="189" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="17"/>
       <c r="B189" s="18"/>
       <c r="C189" s="34"/>
@@ -9246,12 +8949,11 @@
       <c r="U189" s="18"/>
       <c r="V189" s="18"/>
       <c r="W189" s="18"/>
-      <c r="X189" s="18"/>
-      <c r="Y189" s="25"/>
-      <c r="Z189" s="28"/>
-      <c r="AA189" s="23"/>
-    </row>
-    <row r="190" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X189" s="25"/>
+      <c r="Y189" s="28"/>
+      <c r="Z189" s="23"/>
+    </row>
+    <row r="190" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="17"/>
       <c r="B190" s="18"/>
       <c r="C190" s="34"/>
@@ -9275,12 +8977,11 @@
       <c r="U190" s="18"/>
       <c r="V190" s="18"/>
       <c r="W190" s="18"/>
-      <c r="X190" s="18"/>
-      <c r="Y190" s="25"/>
-      <c r="Z190" s="28"/>
-      <c r="AA190" s="23"/>
-    </row>
-    <row r="191" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X190" s="25"/>
+      <c r="Y190" s="28"/>
+      <c r="Z190" s="23"/>
+    </row>
+    <row r="191" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="17"/>
       <c r="B191" s="18"/>
       <c r="C191" s="34"/>
@@ -9304,12 +9005,11 @@
       <c r="U191" s="18"/>
       <c r="V191" s="18"/>
       <c r="W191" s="18"/>
-      <c r="X191" s="18"/>
-      <c r="Y191" s="25"/>
-      <c r="Z191" s="28"/>
-      <c r="AA191" s="23"/>
-    </row>
-    <row r="192" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X191" s="25"/>
+      <c r="Y191" s="28"/>
+      <c r="Z191" s="23"/>
+    </row>
+    <row r="192" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="17"/>
       <c r="B192" s="18"/>
       <c r="C192" s="34"/>
@@ -9333,12 +9033,11 @@
       <c r="U192" s="18"/>
       <c r="V192" s="18"/>
       <c r="W192" s="18"/>
-      <c r="X192" s="18"/>
-      <c r="Y192" s="25"/>
-      <c r="Z192" s="28"/>
-      <c r="AA192" s="23"/>
-    </row>
-    <row r="193" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X192" s="25"/>
+      <c r="Y192" s="28"/>
+      <c r="Z192" s="23"/>
+    </row>
+    <row r="193" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="17"/>
       <c r="B193" s="18"/>
       <c r="C193" s="34"/>
@@ -9362,12 +9061,11 @@
       <c r="U193" s="18"/>
       <c r="V193" s="18"/>
       <c r="W193" s="18"/>
-      <c r="X193" s="18"/>
-      <c r="Y193" s="25"/>
-      <c r="Z193" s="28"/>
-      <c r="AA193" s="23"/>
-    </row>
-    <row r="194" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X193" s="25"/>
+      <c r="Y193" s="28"/>
+      <c r="Z193" s="23"/>
+    </row>
+    <row r="194" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="17"/>
       <c r="B194" s="18"/>
       <c r="C194" s="34"/>
@@ -9391,12 +9089,11 @@
       <c r="U194" s="18"/>
       <c r="V194" s="18"/>
       <c r="W194" s="18"/>
-      <c r="X194" s="18"/>
-      <c r="Y194" s="25"/>
-      <c r="Z194" s="28"/>
-      <c r="AA194" s="23"/>
-    </row>
-    <row r="195" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X194" s="25"/>
+      <c r="Y194" s="28"/>
+      <c r="Z194" s="23"/>
+    </row>
+    <row r="195" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="17"/>
       <c r="B195" s="18"/>
       <c r="C195" s="34"/>
@@ -9420,12 +9117,11 @@
       <c r="U195" s="18"/>
       <c r="V195" s="18"/>
       <c r="W195" s="18"/>
-      <c r="X195" s="18"/>
-      <c r="Y195" s="25"/>
-      <c r="Z195" s="28"/>
-      <c r="AA195" s="23"/>
-    </row>
-    <row r="196" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X195" s="25"/>
+      <c r="Y195" s="28"/>
+      <c r="Z195" s="23"/>
+    </row>
+    <row r="196" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="17"/>
       <c r="B196" s="18"/>
       <c r="C196" s="34"/>
@@ -9449,12 +9145,11 @@
       <c r="U196" s="18"/>
       <c r="V196" s="18"/>
       <c r="W196" s="18"/>
-      <c r="X196" s="18"/>
-      <c r="Y196" s="25"/>
-      <c r="Z196" s="28"/>
-      <c r="AA196" s="23"/>
-    </row>
-    <row r="197" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X196" s="25"/>
+      <c r="Y196" s="28"/>
+      <c r="Z196" s="23"/>
+    </row>
+    <row r="197" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="17"/>
       <c r="B197" s="18"/>
       <c r="C197" s="34"/>
@@ -9478,12 +9173,11 @@
       <c r="U197" s="18"/>
       <c r="V197" s="18"/>
       <c r="W197" s="18"/>
-      <c r="X197" s="18"/>
-      <c r="Y197" s="25"/>
-      <c r="Z197" s="28"/>
-      <c r="AA197" s="23"/>
-    </row>
-    <row r="198" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X197" s="25"/>
+      <c r="Y197" s="28"/>
+      <c r="Z197" s="23"/>
+    </row>
+    <row r="198" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="17"/>
       <c r="B198" s="18"/>
       <c r="C198" s="34"/>
@@ -9507,12 +9201,11 @@
       <c r="U198" s="18"/>
       <c r="V198" s="18"/>
       <c r="W198" s="18"/>
-      <c r="X198" s="18"/>
-      <c r="Y198" s="25"/>
-      <c r="Z198" s="28"/>
-      <c r="AA198" s="23"/>
-    </row>
-    <row r="199" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X198" s="25"/>
+      <c r="Y198" s="28"/>
+      <c r="Z198" s="23"/>
+    </row>
+    <row r="199" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="17"/>
       <c r="B199" s="18"/>
       <c r="C199" s="34"/>
@@ -9536,12 +9229,11 @@
       <c r="U199" s="18"/>
       <c r="V199" s="18"/>
       <c r="W199" s="18"/>
-      <c r="X199" s="18"/>
-      <c r="Y199" s="25"/>
-      <c r="Z199" s="28"/>
-      <c r="AA199" s="23"/>
-    </row>
-    <row r="200" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X199" s="25"/>
+      <c r="Y199" s="28"/>
+      <c r="Z199" s="23"/>
+    </row>
+    <row r="200" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="17"/>
       <c r="B200" s="18"/>
       <c r="C200" s="34"/>
@@ -9565,12 +9257,11 @@
       <c r="U200" s="18"/>
       <c r="V200" s="18"/>
       <c r="W200" s="18"/>
-      <c r="X200" s="18"/>
-      <c r="Y200" s="25"/>
-      <c r="Z200" s="28"/>
-      <c r="AA200" s="23"/>
-    </row>
-    <row r="201" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X200" s="25"/>
+      <c r="Y200" s="28"/>
+      <c r="Z200" s="23"/>
+    </row>
+    <row r="201" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="17"/>
       <c r="B201" s="18"/>
       <c r="C201" s="34"/>
@@ -9594,12 +9285,11 @@
       <c r="U201" s="18"/>
       <c r="V201" s="18"/>
       <c r="W201" s="18"/>
-      <c r="X201" s="18"/>
-      <c r="Y201" s="25"/>
-      <c r="Z201" s="28"/>
-      <c r="AA201" s="23"/>
-    </row>
-    <row r="202" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X201" s="25"/>
+      <c r="Y201" s="28"/>
+      <c r="Z201" s="23"/>
+    </row>
+    <row r="202" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="17"/>
       <c r="B202" s="18"/>
       <c r="C202" s="34"/>
@@ -9623,12 +9313,11 @@
       <c r="U202" s="18"/>
       <c r="V202" s="18"/>
       <c r="W202" s="18"/>
-      <c r="X202" s="18"/>
-      <c r="Y202" s="25"/>
-      <c r="Z202" s="28"/>
-      <c r="AA202" s="23"/>
-    </row>
-    <row r="203" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X202" s="25"/>
+      <c r="Y202" s="28"/>
+      <c r="Z202" s="23"/>
+    </row>
+    <row r="203" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="17"/>
       <c r="B203" s="18"/>
       <c r="C203" s="34"/>
@@ -9652,12 +9341,11 @@
       <c r="U203" s="18"/>
       <c r="V203" s="18"/>
       <c r="W203" s="18"/>
-      <c r="X203" s="18"/>
-      <c r="Y203" s="25"/>
-      <c r="Z203" s="28"/>
-      <c r="AA203" s="23"/>
-    </row>
-    <row r="204" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X203" s="25"/>
+      <c r="Y203" s="28"/>
+      <c r="Z203" s="23"/>
+    </row>
+    <row r="204" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="17"/>
       <c r="B204" s="18"/>
       <c r="C204" s="34"/>
@@ -9681,12 +9369,11 @@
       <c r="U204" s="18"/>
       <c r="V204" s="18"/>
       <c r="W204" s="18"/>
-      <c r="X204" s="18"/>
-      <c r="Y204" s="25"/>
-      <c r="Z204" s="28"/>
-      <c r="AA204" s="23"/>
-    </row>
-    <row r="205" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X204" s="25"/>
+      <c r="Y204" s="28"/>
+      <c r="Z204" s="23"/>
+    </row>
+    <row r="205" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="17"/>
       <c r="B205" s="18"/>
       <c r="C205" s="34"/>
@@ -9710,12 +9397,11 @@
       <c r="U205" s="18"/>
       <c r="V205" s="18"/>
       <c r="W205" s="18"/>
-      <c r="X205" s="18"/>
-      <c r="Y205" s="25"/>
-      <c r="Z205" s="28"/>
-      <c r="AA205" s="23"/>
-    </row>
-    <row r="206" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X205" s="25"/>
+      <c r="Y205" s="28"/>
+      <c r="Z205" s="23"/>
+    </row>
+    <row r="206" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="17"/>
       <c r="B206" s="18"/>
       <c r="C206" s="34"/>
@@ -9739,12 +9425,11 @@
       <c r="U206" s="18"/>
       <c r="V206" s="18"/>
       <c r="W206" s="18"/>
-      <c r="X206" s="18"/>
-      <c r="Y206" s="25"/>
-      <c r="Z206" s="28"/>
-      <c r="AA206" s="23"/>
-    </row>
-    <row r="207" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X206" s="25"/>
+      <c r="Y206" s="28"/>
+      <c r="Z206" s="23"/>
+    </row>
+    <row r="207" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="17"/>
       <c r="B207" s="18"/>
       <c r="C207" s="34"/>
@@ -9768,12 +9453,11 @@
       <c r="U207" s="18"/>
       <c r="V207" s="18"/>
       <c r="W207" s="18"/>
-      <c r="X207" s="18"/>
-      <c r="Y207" s="25"/>
-      <c r="Z207" s="28"/>
-      <c r="AA207" s="23"/>
-    </row>
-    <row r="208" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X207" s="25"/>
+      <c r="Y207" s="28"/>
+      <c r="Z207" s="23"/>
+    </row>
+    <row r="208" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="17"/>
       <c r="B208" s="18"/>
       <c r="C208" s="34"/>
@@ -9797,12 +9481,11 @@
       <c r="U208" s="18"/>
       <c r="V208" s="18"/>
       <c r="W208" s="18"/>
-      <c r="X208" s="18"/>
-      <c r="Y208" s="25"/>
-      <c r="Z208" s="28"/>
-      <c r="AA208" s="23"/>
-    </row>
-    <row r="209" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X208" s="25"/>
+      <c r="Y208" s="28"/>
+      <c r="Z208" s="23"/>
+    </row>
+    <row r="209" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="17"/>
       <c r="B209" s="18"/>
       <c r="C209" s="34"/>
@@ -9826,12 +9509,11 @@
       <c r="U209" s="18"/>
       <c r="V209" s="18"/>
       <c r="W209" s="18"/>
-      <c r="X209" s="18"/>
-      <c r="Y209" s="25"/>
-      <c r="Z209" s="28"/>
-      <c r="AA209" s="23"/>
-    </row>
-    <row r="210" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X209" s="25"/>
+      <c r="Y209" s="28"/>
+      <c r="Z209" s="23"/>
+    </row>
+    <row r="210" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="17"/>
       <c r="B210" s="18"/>
       <c r="C210" s="34"/>
@@ -9855,12 +9537,11 @@
       <c r="U210" s="18"/>
       <c r="V210" s="18"/>
       <c r="W210" s="18"/>
-      <c r="X210" s="18"/>
-      <c r="Y210" s="25"/>
-      <c r="Z210" s="28"/>
-      <c r="AA210" s="23"/>
-    </row>
-    <row r="211" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X210" s="25"/>
+      <c r="Y210" s="28"/>
+      <c r="Z210" s="23"/>
+    </row>
+    <row r="211" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="17"/>
       <c r="B211" s="18"/>
       <c r="C211" s="34"/>
@@ -9884,12 +9565,11 @@
       <c r="U211" s="18"/>
       <c r="V211" s="18"/>
       <c r="W211" s="18"/>
-      <c r="X211" s="18"/>
-      <c r="Y211" s="25"/>
-      <c r="Z211" s="28"/>
-      <c r="AA211" s="23"/>
-    </row>
-    <row r="212" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X211" s="25"/>
+      <c r="Y211" s="28"/>
+      <c r="Z211" s="23"/>
+    </row>
+    <row r="212" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="17"/>
       <c r="B212" s="18"/>
       <c r="C212" s="34"/>
@@ -9913,12 +9593,11 @@
       <c r="U212" s="18"/>
       <c r="V212" s="18"/>
       <c r="W212" s="18"/>
-      <c r="X212" s="18"/>
-      <c r="Y212" s="25"/>
-      <c r="Z212" s="28"/>
-      <c r="AA212" s="23"/>
-    </row>
-    <row r="213" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X212" s="25"/>
+      <c r="Y212" s="28"/>
+      <c r="Z212" s="23"/>
+    </row>
+    <row r="213" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="17"/>
       <c r="B213" s="18"/>
       <c r="C213" s="34"/>
@@ -9942,12 +9621,11 @@
       <c r="U213" s="18"/>
       <c r="V213" s="18"/>
       <c r="W213" s="18"/>
-      <c r="X213" s="18"/>
-      <c r="Y213" s="25"/>
-      <c r="Z213" s="28"/>
-      <c r="AA213" s="23"/>
-    </row>
-    <row r="214" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X213" s="25"/>
+      <c r="Y213" s="28"/>
+      <c r="Z213" s="23"/>
+    </row>
+    <row r="214" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="17"/>
       <c r="B214" s="18"/>
       <c r="C214" s="34"/>
@@ -9971,12 +9649,11 @@
       <c r="U214" s="18"/>
       <c r="V214" s="18"/>
       <c r="W214" s="18"/>
-      <c r="X214" s="18"/>
-      <c r="Y214" s="25"/>
-      <c r="Z214" s="28"/>
-      <c r="AA214" s="23"/>
-    </row>
-    <row r="215" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X214" s="25"/>
+      <c r="Y214" s="28"/>
+      <c r="Z214" s="23"/>
+    </row>
+    <row r="215" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="17"/>
       <c r="B215" s="18"/>
       <c r="C215" s="34"/>
@@ -10000,12 +9677,11 @@
       <c r="U215" s="18"/>
       <c r="V215" s="18"/>
       <c r="W215" s="18"/>
-      <c r="X215" s="18"/>
-      <c r="Y215" s="25"/>
-      <c r="Z215" s="28"/>
-      <c r="AA215" s="23"/>
-    </row>
-    <row r="216" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X215" s="25"/>
+      <c r="Y215" s="28"/>
+      <c r="Z215" s="23"/>
+    </row>
+    <row r="216" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="17"/>
       <c r="B216" s="18"/>
       <c r="C216" s="34"/>
@@ -10029,12 +9705,11 @@
       <c r="U216" s="18"/>
       <c r="V216" s="18"/>
       <c r="W216" s="18"/>
-      <c r="X216" s="18"/>
-      <c r="Y216" s="25"/>
-      <c r="Z216" s="28"/>
-      <c r="AA216" s="23"/>
-    </row>
-    <row r="217" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X216" s="25"/>
+      <c r="Y216" s="28"/>
+      <c r="Z216" s="23"/>
+    </row>
+    <row r="217" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="17"/>
       <c r="B217" s="18"/>
       <c r="C217" s="34"/>
@@ -10058,12 +9733,11 @@
       <c r="U217" s="18"/>
       <c r="V217" s="18"/>
       <c r="W217" s="18"/>
-      <c r="X217" s="18"/>
-      <c r="Y217" s="25"/>
-      <c r="Z217" s="28"/>
-      <c r="AA217" s="23"/>
-    </row>
-    <row r="218" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X217" s="25"/>
+      <c r="Y217" s="28"/>
+      <c r="Z217" s="23"/>
+    </row>
+    <row r="218" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="17"/>
       <c r="B218" s="18"/>
       <c r="C218" s="34"/>
@@ -10087,12 +9761,11 @@
       <c r="U218" s="18"/>
       <c r="V218" s="18"/>
       <c r="W218" s="18"/>
-      <c r="X218" s="18"/>
-      <c r="Y218" s="25"/>
-      <c r="Z218" s="28"/>
-      <c r="AA218" s="23"/>
-    </row>
-    <row r="219" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X218" s="25"/>
+      <c r="Y218" s="28"/>
+      <c r="Z218" s="23"/>
+    </row>
+    <row r="219" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="17"/>
       <c r="B219" s="18"/>
       <c r="C219" s="34"/>
@@ -10116,12 +9789,11 @@
       <c r="U219" s="18"/>
       <c r="V219" s="18"/>
       <c r="W219" s="18"/>
-      <c r="X219" s="18"/>
-      <c r="Y219" s="25"/>
-      <c r="Z219" s="28"/>
-      <c r="AA219" s="23"/>
-    </row>
-    <row r="220" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X219" s="25"/>
+      <c r="Y219" s="28"/>
+      <c r="Z219" s="23"/>
+    </row>
+    <row r="220" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="17"/>
       <c r="B220" s="18"/>
       <c r="C220" s="34"/>
@@ -10145,12 +9817,11 @@
       <c r="U220" s="18"/>
       <c r="V220" s="18"/>
       <c r="W220" s="18"/>
-      <c r="X220" s="18"/>
-      <c r="Y220" s="25"/>
-      <c r="Z220" s="28"/>
-      <c r="AA220" s="23"/>
-    </row>
-    <row r="221" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X220" s="25"/>
+      <c r="Y220" s="28"/>
+      <c r="Z220" s="23"/>
+    </row>
+    <row r="221" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="17"/>
       <c r="B221" s="18"/>
       <c r="C221" s="34"/>
@@ -10174,12 +9845,11 @@
       <c r="U221" s="18"/>
       <c r="V221" s="18"/>
       <c r="W221" s="18"/>
-      <c r="X221" s="18"/>
-      <c r="Y221" s="25"/>
-      <c r="Z221" s="28"/>
-      <c r="AA221" s="23"/>
-    </row>
-    <row r="222" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X221" s="25"/>
+      <c r="Y221" s="28"/>
+      <c r="Z221" s="23"/>
+    </row>
+    <row r="222" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="17"/>
       <c r="B222" s="18"/>
       <c r="C222" s="34"/>
@@ -10203,12 +9873,11 @@
       <c r="U222" s="18"/>
       <c r="V222" s="18"/>
       <c r="W222" s="18"/>
-      <c r="X222" s="18"/>
-      <c r="Y222" s="25"/>
-      <c r="Z222" s="28"/>
-      <c r="AA222" s="23"/>
-    </row>
-    <row r="223" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X222" s="25"/>
+      <c r="Y222" s="28"/>
+      <c r="Z222" s="23"/>
+    </row>
+    <row r="223" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="17"/>
       <c r="B223" s="18"/>
       <c r="C223" s="34"/>
@@ -10232,12 +9901,11 @@
       <c r="U223" s="18"/>
       <c r="V223" s="18"/>
       <c r="W223" s="18"/>
-      <c r="X223" s="18"/>
-      <c r="Y223" s="25"/>
-      <c r="Z223" s="28"/>
-      <c r="AA223" s="23"/>
-    </row>
-    <row r="224" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X223" s="25"/>
+      <c r="Y223" s="28"/>
+      <c r="Z223" s="23"/>
+    </row>
+    <row r="224" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="17"/>
       <c r="B224" s="18"/>
       <c r="C224" s="34"/>
@@ -10261,12 +9929,11 @@
       <c r="U224" s="18"/>
       <c r="V224" s="18"/>
       <c r="W224" s="18"/>
-      <c r="X224" s="18"/>
-      <c r="Y224" s="25"/>
-      <c r="Z224" s="28"/>
-      <c r="AA224" s="23"/>
-    </row>
-    <row r="225" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X224" s="25"/>
+      <c r="Y224" s="28"/>
+      <c r="Z224" s="23"/>
+    </row>
+    <row r="225" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="17"/>
       <c r="B225" s="18"/>
       <c r="C225" s="34"/>
@@ -10290,12 +9957,11 @@
       <c r="U225" s="18"/>
       <c r="V225" s="18"/>
       <c r="W225" s="18"/>
-      <c r="X225" s="18"/>
-      <c r="Y225" s="25"/>
-      <c r="Z225" s="28"/>
-      <c r="AA225" s="23"/>
-    </row>
-    <row r="226" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X225" s="25"/>
+      <c r="Y225" s="28"/>
+      <c r="Z225" s="23"/>
+    </row>
+    <row r="226" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="17"/>
       <c r="B226" s="18"/>
       <c r="C226" s="34"/>
@@ -10319,12 +9985,11 @@
       <c r="U226" s="18"/>
       <c r="V226" s="18"/>
       <c r="W226" s="18"/>
-      <c r="X226" s="18"/>
-      <c r="Y226" s="25"/>
-      <c r="Z226" s="28"/>
-      <c r="AA226" s="23"/>
-    </row>
-    <row r="227" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X226" s="25"/>
+      <c r="Y226" s="28"/>
+      <c r="Z226" s="23"/>
+    </row>
+    <row r="227" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="17"/>
       <c r="B227" s="18"/>
       <c r="C227" s="34"/>
@@ -10348,12 +10013,11 @@
       <c r="U227" s="18"/>
       <c r="V227" s="18"/>
       <c r="W227" s="18"/>
-      <c r="X227" s="18"/>
-      <c r="Y227" s="25"/>
-      <c r="Z227" s="28"/>
-      <c r="AA227" s="23"/>
-    </row>
-    <row r="228" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X227" s="25"/>
+      <c r="Y227" s="28"/>
+      <c r="Z227" s="23"/>
+    </row>
+    <row r="228" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="17"/>
       <c r="B228" s="18"/>
       <c r="C228" s="34"/>
@@ -10377,12 +10041,11 @@
       <c r="U228" s="18"/>
       <c r="V228" s="18"/>
       <c r="W228" s="18"/>
-      <c r="X228" s="18"/>
-      <c r="Y228" s="25"/>
-      <c r="Z228" s="28"/>
-      <c r="AA228" s="23"/>
-    </row>
-    <row r="229" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X228" s="25"/>
+      <c r="Y228" s="28"/>
+      <c r="Z228" s="23"/>
+    </row>
+    <row r="229" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="17"/>
       <c r="B229" s="18"/>
       <c r="C229" s="34"/>
@@ -10406,12 +10069,11 @@
       <c r="U229" s="18"/>
       <c r="V229" s="18"/>
       <c r="W229" s="18"/>
-      <c r="X229" s="18"/>
-      <c r="Y229" s="25"/>
-      <c r="Z229" s="28"/>
-      <c r="AA229" s="23"/>
-    </row>
-    <row r="230" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X229" s="25"/>
+      <c r="Y229" s="28"/>
+      <c r="Z229" s="23"/>
+    </row>
+    <row r="230" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="17"/>
       <c r="B230" s="18"/>
       <c r="C230" s="34"/>
@@ -10435,12 +10097,11 @@
       <c r="U230" s="18"/>
       <c r="V230" s="18"/>
       <c r="W230" s="18"/>
-      <c r="X230" s="18"/>
-      <c r="Y230" s="25"/>
-      <c r="Z230" s="28"/>
-      <c r="AA230" s="23"/>
-    </row>
-    <row r="231" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X230" s="25"/>
+      <c r="Y230" s="28"/>
+      <c r="Z230" s="23"/>
+    </row>
+    <row r="231" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="17"/>
       <c r="B231" s="18"/>
       <c r="C231" s="34"/>
@@ -10464,12 +10125,11 @@
       <c r="U231" s="18"/>
       <c r="V231" s="18"/>
       <c r="W231" s="18"/>
-      <c r="X231" s="18"/>
-      <c r="Y231" s="25"/>
-      <c r="Z231" s="28"/>
-      <c r="AA231" s="23"/>
-    </row>
-    <row r="232" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X231" s="25"/>
+      <c r="Y231" s="28"/>
+      <c r="Z231" s="23"/>
+    </row>
+    <row r="232" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="17"/>
       <c r="B232" s="18"/>
       <c r="C232" s="34"/>
@@ -10493,12 +10153,11 @@
       <c r="U232" s="18"/>
       <c r="V232" s="18"/>
       <c r="W232" s="18"/>
-      <c r="X232" s="18"/>
-      <c r="Y232" s="25"/>
-      <c r="Z232" s="28"/>
-      <c r="AA232" s="23"/>
-    </row>
-    <row r="233" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X232" s="25"/>
+      <c r="Y232" s="28"/>
+      <c r="Z232" s="23"/>
+    </row>
+    <row r="233" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="17"/>
       <c r="B233" s="18"/>
       <c r="C233" s="34"/>
@@ -10522,12 +10181,11 @@
       <c r="U233" s="18"/>
       <c r="V233" s="18"/>
       <c r="W233" s="18"/>
-      <c r="X233" s="18"/>
-      <c r="Y233" s="25"/>
-      <c r="Z233" s="28"/>
-      <c r="AA233" s="23"/>
-    </row>
-    <row r="234" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X233" s="25"/>
+      <c r="Y233" s="28"/>
+      <c r="Z233" s="23"/>
+    </row>
+    <row r="234" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="17"/>
       <c r="B234" s="18"/>
       <c r="C234" s="34"/>
@@ -10551,12 +10209,11 @@
       <c r="U234" s="18"/>
       <c r="V234" s="18"/>
       <c r="W234" s="18"/>
-      <c r="X234" s="18"/>
-      <c r="Y234" s="25"/>
-      <c r="Z234" s="28"/>
-      <c r="AA234" s="23"/>
-    </row>
-    <row r="235" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X234" s="25"/>
+      <c r="Y234" s="28"/>
+      <c r="Z234" s="23"/>
+    </row>
+    <row r="235" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="17"/>
       <c r="B235" s="18"/>
       <c r="C235" s="34"/>
@@ -10580,12 +10237,11 @@
       <c r="U235" s="18"/>
       <c r="V235" s="18"/>
       <c r="W235" s="18"/>
-      <c r="X235" s="18"/>
-      <c r="Y235" s="25"/>
-      <c r="Z235" s="28"/>
-      <c r="AA235" s="23"/>
-    </row>
-    <row r="236" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X235" s="25"/>
+      <c r="Y235" s="28"/>
+      <c r="Z235" s="23"/>
+    </row>
+    <row r="236" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="17"/>
       <c r="B236" s="18"/>
       <c r="C236" s="34"/>
@@ -10609,12 +10265,11 @@
       <c r="U236" s="18"/>
       <c r="V236" s="18"/>
       <c r="W236" s="18"/>
-      <c r="X236" s="18"/>
-      <c r="Y236" s="25"/>
-      <c r="Z236" s="28"/>
-      <c r="AA236" s="23"/>
-    </row>
-    <row r="237" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X236" s="25"/>
+      <c r="Y236" s="28"/>
+      <c r="Z236" s="23"/>
+    </row>
+    <row r="237" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="17"/>
       <c r="B237" s="18"/>
       <c r="C237" s="34"/>
@@ -10638,12 +10293,11 @@
       <c r="U237" s="18"/>
       <c r="V237" s="18"/>
       <c r="W237" s="18"/>
-      <c r="X237" s="18"/>
-      <c r="Y237" s="25"/>
-      <c r="Z237" s="28"/>
-      <c r="AA237" s="23"/>
-    </row>
-    <row r="238" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X237" s="25"/>
+      <c r="Y237" s="28"/>
+      <c r="Z237" s="23"/>
+    </row>
+    <row r="238" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="17"/>
       <c r="B238" s="18"/>
       <c r="C238" s="34"/>
@@ -10667,12 +10321,11 @@
       <c r="U238" s="18"/>
       <c r="V238" s="18"/>
       <c r="W238" s="18"/>
-      <c r="X238" s="18"/>
-      <c r="Y238" s="25"/>
-      <c r="Z238" s="28"/>
-      <c r="AA238" s="23"/>
-    </row>
-    <row r="239" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X238" s="25"/>
+      <c r="Y238" s="28"/>
+      <c r="Z238" s="23"/>
+    </row>
+    <row r="239" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="17"/>
       <c r="B239" s="18"/>
       <c r="C239" s="34"/>
@@ -10696,12 +10349,11 @@
       <c r="U239" s="18"/>
       <c r="V239" s="18"/>
       <c r="W239" s="18"/>
-      <c r="X239" s="18"/>
-      <c r="Y239" s="25"/>
-      <c r="Z239" s="28"/>
-      <c r="AA239" s="23"/>
-    </row>
-    <row r="240" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X239" s="25"/>
+      <c r="Y239" s="28"/>
+      <c r="Z239" s="23"/>
+    </row>
+    <row r="240" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="17"/>
       <c r="B240" s="18"/>
       <c r="C240" s="34"/>
@@ -10725,12 +10377,11 @@
       <c r="U240" s="18"/>
       <c r="V240" s="18"/>
       <c r="W240" s="18"/>
-      <c r="X240" s="18"/>
-      <c r="Y240" s="25"/>
-      <c r="Z240" s="28"/>
-      <c r="AA240" s="23"/>
-    </row>
-    <row r="241" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X240" s="25"/>
+      <c r="Y240" s="28"/>
+      <c r="Z240" s="23"/>
+    </row>
+    <row r="241" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="17"/>
       <c r="B241" s="18"/>
       <c r="C241" s="34"/>
@@ -10754,12 +10405,11 @@
       <c r="U241" s="18"/>
       <c r="V241" s="18"/>
       <c r="W241" s="18"/>
-      <c r="X241" s="18"/>
-      <c r="Y241" s="25"/>
-      <c r="Z241" s="28"/>
-      <c r="AA241" s="23"/>
-    </row>
-    <row r="242" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X241" s="25"/>
+      <c r="Y241" s="28"/>
+      <c r="Z241" s="23"/>
+    </row>
+    <row r="242" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="17"/>
       <c r="B242" s="18"/>
       <c r="C242" s="34"/>
@@ -10783,12 +10433,11 @@
       <c r="U242" s="18"/>
       <c r="V242" s="18"/>
       <c r="W242" s="18"/>
-      <c r="X242" s="18"/>
-      <c r="Y242" s="25"/>
-      <c r="Z242" s="28"/>
-      <c r="AA242" s="23"/>
-    </row>
-    <row r="243" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X242" s="25"/>
+      <c r="Y242" s="28"/>
+      <c r="Z242" s="23"/>
+    </row>
+    <row r="243" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="17"/>
       <c r="B243" s="18"/>
       <c r="C243" s="34"/>
@@ -10812,12 +10461,11 @@
       <c r="U243" s="18"/>
       <c r="V243" s="18"/>
       <c r="W243" s="18"/>
-      <c r="X243" s="18"/>
-      <c r="Y243" s="25"/>
-      <c r="Z243" s="28"/>
-      <c r="AA243" s="23"/>
-    </row>
-    <row r="244" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X243" s="25"/>
+      <c r="Y243" s="28"/>
+      <c r="Z243" s="23"/>
+    </row>
+    <row r="244" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="17"/>
       <c r="B244" s="18"/>
       <c r="C244" s="34"/>
@@ -10841,12 +10489,11 @@
       <c r="U244" s="18"/>
       <c r="V244" s="18"/>
       <c r="W244" s="18"/>
-      <c r="X244" s="18"/>
-      <c r="Y244" s="25"/>
-      <c r="Z244" s="28"/>
-      <c r="AA244" s="23"/>
-    </row>
-    <row r="245" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X244" s="25"/>
+      <c r="Y244" s="28"/>
+      <c r="Z244" s="23"/>
+    </row>
+    <row r="245" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="17"/>
       <c r="B245" s="18"/>
       <c r="C245" s="34"/>
@@ -10870,12 +10517,11 @@
       <c r="U245" s="18"/>
       <c r="V245" s="18"/>
       <c r="W245" s="18"/>
-      <c r="X245" s="18"/>
-      <c r="Y245" s="25"/>
-      <c r="Z245" s="28"/>
-      <c r="AA245" s="23"/>
-    </row>
-    <row r="246" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X245" s="25"/>
+      <c r="Y245" s="28"/>
+      <c r="Z245" s="23"/>
+    </row>
+    <row r="246" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="17"/>
       <c r="B246" s="18"/>
       <c r="C246" s="34"/>
@@ -10899,12 +10545,11 @@
       <c r="U246" s="18"/>
       <c r="V246" s="18"/>
       <c r="W246" s="18"/>
-      <c r="X246" s="18"/>
-      <c r="Y246" s="25"/>
-      <c r="Z246" s="28"/>
-      <c r="AA246" s="23"/>
-    </row>
-    <row r="247" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X246" s="25"/>
+      <c r="Y246" s="28"/>
+      <c r="Z246" s="23"/>
+    </row>
+    <row r="247" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="17"/>
       <c r="B247" s="18"/>
       <c r="C247" s="34"/>
@@ -10928,12 +10573,11 @@
       <c r="U247" s="18"/>
       <c r="V247" s="18"/>
       <c r="W247" s="18"/>
-      <c r="X247" s="18"/>
-      <c r="Y247" s="25"/>
-      <c r="Z247" s="28"/>
-      <c r="AA247" s="23"/>
-    </row>
-    <row r="248" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X247" s="25"/>
+      <c r="Y247" s="28"/>
+      <c r="Z247" s="23"/>
+    </row>
+    <row r="248" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="17"/>
       <c r="B248" s="18"/>
       <c r="C248" s="34"/>
@@ -10957,12 +10601,11 @@
       <c r="U248" s="18"/>
       <c r="V248" s="18"/>
       <c r="W248" s="18"/>
-      <c r="X248" s="18"/>
-      <c r="Y248" s="25"/>
-      <c r="Z248" s="28"/>
-      <c r="AA248" s="23"/>
-    </row>
-    <row r="249" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X248" s="25"/>
+      <c r="Y248" s="28"/>
+      <c r="Z248" s="23"/>
+    </row>
+    <row r="249" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="17"/>
       <c r="B249" s="18"/>
       <c r="C249" s="34"/>
@@ -10986,12 +10629,11 @@
       <c r="U249" s="18"/>
       <c r="V249" s="18"/>
       <c r="W249" s="18"/>
-      <c r="X249" s="18"/>
-      <c r="Y249" s="25"/>
-      <c r="Z249" s="28"/>
-      <c r="AA249" s="23"/>
-    </row>
-    <row r="250" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X249" s="25"/>
+      <c r="Y249" s="28"/>
+      <c r="Z249" s="23"/>
+    </row>
+    <row r="250" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="17"/>
       <c r="B250" s="18"/>
       <c r="C250" s="34"/>
@@ -11015,12 +10657,11 @@
       <c r="U250" s="18"/>
       <c r="V250" s="18"/>
       <c r="W250" s="18"/>
-      <c r="X250" s="18"/>
-      <c r="Y250" s="25"/>
-      <c r="Z250" s="28"/>
-      <c r="AA250" s="23"/>
-    </row>
-    <row r="251" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X250" s="25"/>
+      <c r="Y250" s="28"/>
+      <c r="Z250" s="23"/>
+    </row>
+    <row r="251" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="17"/>
       <c r="B251" s="18"/>
       <c r="C251" s="34"/>
@@ -11044,12 +10685,11 @@
       <c r="U251" s="18"/>
       <c r="V251" s="18"/>
       <c r="W251" s="18"/>
-      <c r="X251" s="18"/>
-      <c r="Y251" s="25"/>
-      <c r="Z251" s="28"/>
-      <c r="AA251" s="23"/>
-    </row>
-    <row r="252" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X251" s="25"/>
+      <c r="Y251" s="28"/>
+      <c r="Z251" s="23"/>
+    </row>
+    <row r="252" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="17"/>
       <c r="B252" s="18"/>
       <c r="C252" s="34"/>
@@ -11073,12 +10713,11 @@
       <c r="U252" s="18"/>
       <c r="V252" s="18"/>
       <c r="W252" s="18"/>
-      <c r="X252" s="18"/>
-      <c r="Y252" s="25"/>
-      <c r="Z252" s="28"/>
-      <c r="AA252" s="23"/>
-    </row>
-    <row r="253" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X252" s="25"/>
+      <c r="Y252" s="28"/>
+      <c r="Z252" s="23"/>
+    </row>
+    <row r="253" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="17"/>
       <c r="B253" s="18"/>
       <c r="C253" s="34"/>
@@ -11102,12 +10741,11 @@
       <c r="U253" s="18"/>
       <c r="V253" s="18"/>
       <c r="W253" s="18"/>
-      <c r="X253" s="18"/>
-      <c r="Y253" s="25"/>
-      <c r="Z253" s="28"/>
-      <c r="AA253" s="23"/>
-    </row>
-    <row r="254" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X253" s="25"/>
+      <c r="Y253" s="28"/>
+      <c r="Z253" s="23"/>
+    </row>
+    <row r="254" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="17"/>
       <c r="B254" s="18"/>
       <c r="C254" s="34"/>
@@ -11131,12 +10769,11 @@
       <c r="U254" s="18"/>
       <c r="V254" s="18"/>
       <c r="W254" s="18"/>
-      <c r="X254" s="18"/>
-      <c r="Y254" s="25"/>
-      <c r="Z254" s="28"/>
-      <c r="AA254" s="23"/>
-    </row>
-    <row r="255" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X254" s="25"/>
+      <c r="Y254" s="28"/>
+      <c r="Z254" s="23"/>
+    </row>
+    <row r="255" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="17"/>
       <c r="B255" s="18"/>
       <c r="C255" s="34"/>
@@ -11160,12 +10797,11 @@
       <c r="U255" s="18"/>
       <c r="V255" s="18"/>
       <c r="W255" s="18"/>
-      <c r="X255" s="18"/>
-      <c r="Y255" s="25"/>
-      <c r="Z255" s="28"/>
-      <c r="AA255" s="23"/>
-    </row>
-    <row r="256" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X255" s="25"/>
+      <c r="Y255" s="28"/>
+      <c r="Z255" s="23"/>
+    </row>
+    <row r="256" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="17"/>
       <c r="B256" s="18"/>
       <c r="C256" s="34"/>
@@ -11189,12 +10825,11 @@
       <c r="U256" s="18"/>
       <c r="V256" s="18"/>
       <c r="W256" s="18"/>
-      <c r="X256" s="18"/>
-      <c r="Y256" s="25"/>
-      <c r="Z256" s="28"/>
-      <c r="AA256" s="23"/>
-    </row>
-    <row r="257" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X256" s="25"/>
+      <c r="Y256" s="28"/>
+      <c r="Z256" s="23"/>
+    </row>
+    <row r="257" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="17"/>
       <c r="B257" s="18"/>
       <c r="C257" s="34"/>
@@ -11218,12 +10853,11 @@
       <c r="U257" s="18"/>
       <c r="V257" s="18"/>
       <c r="W257" s="18"/>
-      <c r="X257" s="18"/>
-      <c r="Y257" s="25"/>
-      <c r="Z257" s="28"/>
-      <c r="AA257" s="23"/>
-    </row>
-    <row r="258" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X257" s="25"/>
+      <c r="Y257" s="28"/>
+      <c r="Z257" s="23"/>
+    </row>
+    <row r="258" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="17"/>
       <c r="B258" s="18"/>
       <c r="C258" s="34"/>
@@ -11247,12 +10881,11 @@
       <c r="U258" s="18"/>
       <c r="V258" s="18"/>
       <c r="W258" s="18"/>
-      <c r="X258" s="18"/>
-      <c r="Y258" s="25"/>
-      <c r="Z258" s="28"/>
-      <c r="AA258" s="23"/>
-    </row>
-    <row r="259" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X258" s="25"/>
+      <c r="Y258" s="28"/>
+      <c r="Z258" s="23"/>
+    </row>
+    <row r="259" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="17"/>
       <c r="B259" s="18"/>
       <c r="C259" s="34"/>
@@ -11276,12 +10909,11 @@
       <c r="U259" s="18"/>
       <c r="V259" s="18"/>
       <c r="W259" s="18"/>
-      <c r="X259" s="18"/>
-      <c r="Y259" s="25"/>
-      <c r="Z259" s="28"/>
-      <c r="AA259" s="23"/>
-    </row>
-    <row r="260" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X259" s="25"/>
+      <c r="Y259" s="28"/>
+      <c r="Z259" s="23"/>
+    </row>
+    <row r="260" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="17"/>
       <c r="B260" s="18"/>
       <c r="C260" s="34"/>
@@ -11305,12 +10937,11 @@
       <c r="U260" s="18"/>
       <c r="V260" s="18"/>
       <c r="W260" s="18"/>
-      <c r="X260" s="18"/>
-      <c r="Y260" s="25"/>
-      <c r="Z260" s="28"/>
-      <c r="AA260" s="23"/>
-    </row>
-    <row r="261" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X260" s="25"/>
+      <c r="Y260" s="28"/>
+      <c r="Z260" s="23"/>
+    </row>
+    <row r="261" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="17"/>
       <c r="B261" s="18"/>
       <c r="C261" s="34"/>
@@ -11334,12 +10965,11 @@
       <c r="U261" s="18"/>
       <c r="V261" s="18"/>
       <c r="W261" s="18"/>
-      <c r="X261" s="18"/>
-      <c r="Y261" s="25"/>
-      <c r="Z261" s="28"/>
-      <c r="AA261" s="23"/>
-    </row>
-    <row r="262" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X261" s="25"/>
+      <c r="Y261" s="28"/>
+      <c r="Z261" s="23"/>
+    </row>
+    <row r="262" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="17"/>
       <c r="B262" s="18"/>
       <c r="C262" s="34"/>
@@ -11363,12 +10993,11 @@
       <c r="U262" s="18"/>
       <c r="V262" s="18"/>
       <c r="W262" s="18"/>
-      <c r="X262" s="18"/>
-      <c r="Y262" s="25"/>
-      <c r="Z262" s="28"/>
-      <c r="AA262" s="23"/>
-    </row>
-    <row r="263" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X262" s="25"/>
+      <c r="Y262" s="28"/>
+      <c r="Z262" s="23"/>
+    </row>
+    <row r="263" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="17"/>
       <c r="B263" s="18"/>
       <c r="C263" s="34"/>
@@ -11392,12 +11021,11 @@
       <c r="U263" s="18"/>
       <c r="V263" s="18"/>
       <c r="W263" s="18"/>
-      <c r="X263" s="18"/>
-      <c r="Y263" s="25"/>
-      <c r="Z263" s="28"/>
-      <c r="AA263" s="23"/>
-    </row>
-    <row r="264" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X263" s="25"/>
+      <c r="Y263" s="28"/>
+      <c r="Z263" s="23"/>
+    </row>
+    <row r="264" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="17"/>
       <c r="B264" s="18"/>
       <c r="C264" s="34"/>
@@ -11421,12 +11049,11 @@
       <c r="U264" s="18"/>
       <c r="V264" s="18"/>
       <c r="W264" s="18"/>
-      <c r="X264" s="18"/>
-      <c r="Y264" s="25"/>
-      <c r="Z264" s="28"/>
-      <c r="AA264" s="23"/>
-    </row>
-    <row r="265" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X264" s="25"/>
+      <c r="Y264" s="28"/>
+      <c r="Z264" s="23"/>
+    </row>
+    <row r="265" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="17"/>
       <c r="B265" s="18"/>
       <c r="C265" s="34"/>
@@ -11450,12 +11077,11 @@
       <c r="U265" s="18"/>
       <c r="V265" s="18"/>
       <c r="W265" s="18"/>
-      <c r="X265" s="18"/>
-      <c r="Y265" s="25"/>
-      <c r="Z265" s="28"/>
-      <c r="AA265" s="23"/>
-    </row>
-    <row r="266" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X265" s="25"/>
+      <c r="Y265" s="28"/>
+      <c r="Z265" s="23"/>
+    </row>
+    <row r="266" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="17"/>
       <c r="B266" s="18"/>
       <c r="C266" s="34"/>
@@ -11479,12 +11105,11 @@
       <c r="U266" s="18"/>
       <c r="V266" s="18"/>
       <c r="W266" s="18"/>
-      <c r="X266" s="18"/>
-      <c r="Y266" s="25"/>
-      <c r="Z266" s="28"/>
-      <c r="AA266" s="23"/>
-    </row>
-    <row r="267" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X266" s="25"/>
+      <c r="Y266" s="28"/>
+      <c r="Z266" s="23"/>
+    </row>
+    <row r="267" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="17"/>
       <c r="B267" s="18"/>
       <c r="C267" s="34"/>
@@ -11508,12 +11133,11 @@
       <c r="U267" s="18"/>
       <c r="V267" s="18"/>
       <c r="W267" s="18"/>
-      <c r="X267" s="18"/>
-      <c r="Y267" s="25"/>
-      <c r="Z267" s="28"/>
-      <c r="AA267" s="23"/>
-    </row>
-    <row r="268" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X267" s="25"/>
+      <c r="Y267" s="28"/>
+      <c r="Z267" s="23"/>
+    </row>
+    <row r="268" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="17"/>
       <c r="B268" s="18"/>
       <c r="C268" s="34"/>
@@ -11537,12 +11161,11 @@
       <c r="U268" s="18"/>
       <c r="V268" s="18"/>
       <c r="W268" s="18"/>
-      <c r="X268" s="18"/>
-      <c r="Y268" s="25"/>
-      <c r="Z268" s="28"/>
-      <c r="AA268" s="23"/>
-    </row>
-    <row r="269" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X268" s="25"/>
+      <c r="Y268" s="28"/>
+      <c r="Z268" s="23"/>
+    </row>
+    <row r="269" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="17"/>
       <c r="B269" s="18"/>
       <c r="C269" s="34"/>
@@ -11566,12 +11189,11 @@
       <c r="U269" s="18"/>
       <c r="V269" s="18"/>
       <c r="W269" s="18"/>
-      <c r="X269" s="18"/>
-      <c r="Y269" s="25"/>
-      <c r="Z269" s="28"/>
-      <c r="AA269" s="23"/>
-    </row>
-    <row r="270" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X269" s="25"/>
+      <c r="Y269" s="28"/>
+      <c r="Z269" s="23"/>
+    </row>
+    <row r="270" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="17"/>
       <c r="B270" s="18"/>
       <c r="C270" s="34"/>
@@ -11595,12 +11217,11 @@
       <c r="U270" s="18"/>
       <c r="V270" s="18"/>
       <c r="W270" s="18"/>
-      <c r="X270" s="18"/>
-      <c r="Y270" s="25"/>
-      <c r="Z270" s="28"/>
-      <c r="AA270" s="23"/>
-    </row>
-    <row r="271" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X270" s="25"/>
+      <c r="Y270" s="28"/>
+      <c r="Z270" s="23"/>
+    </row>
+    <row r="271" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="17"/>
       <c r="B271" s="18"/>
       <c r="C271" s="34"/>
@@ -11624,12 +11245,11 @@
       <c r="U271" s="18"/>
       <c r="V271" s="18"/>
       <c r="W271" s="18"/>
-      <c r="X271" s="18"/>
-      <c r="Y271" s="25"/>
-      <c r="Z271" s="28"/>
-      <c r="AA271" s="23"/>
-    </row>
-    <row r="272" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X271" s="25"/>
+      <c r="Y271" s="28"/>
+      <c r="Z271" s="23"/>
+    </row>
+    <row r="272" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="17"/>
       <c r="B272" s="18"/>
       <c r="C272" s="34"/>
@@ -11653,12 +11273,11 @@
       <c r="U272" s="18"/>
       <c r="V272" s="18"/>
       <c r="W272" s="18"/>
-      <c r="X272" s="18"/>
-      <c r="Y272" s="25"/>
-      <c r="Z272" s="28"/>
-      <c r="AA272" s="23"/>
-    </row>
-    <row r="273" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X272" s="25"/>
+      <c r="Y272" s="28"/>
+      <c r="Z272" s="23"/>
+    </row>
+    <row r="273" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="17"/>
       <c r="B273" s="18"/>
       <c r="C273" s="34"/>
@@ -11682,12 +11301,11 @@
       <c r="U273" s="18"/>
       <c r="V273" s="18"/>
       <c r="W273" s="18"/>
-      <c r="X273" s="18"/>
-      <c r="Y273" s="25"/>
-      <c r="Z273" s="28"/>
-      <c r="AA273" s="23"/>
-    </row>
-    <row r="274" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X273" s="25"/>
+      <c r="Y273" s="28"/>
+      <c r="Z273" s="23"/>
+    </row>
+    <row r="274" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="17"/>
       <c r="B274" s="18"/>
       <c r="C274" s="34"/>
@@ -11711,12 +11329,11 @@
       <c r="U274" s="18"/>
       <c r="V274" s="18"/>
       <c r="W274" s="18"/>
-      <c r="X274" s="18"/>
-      <c r="Y274" s="25"/>
-      <c r="Z274" s="28"/>
-      <c r="AA274" s="23"/>
-    </row>
-    <row r="275" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X274" s="25"/>
+      <c r="Y274" s="28"/>
+      <c r="Z274" s="23"/>
+    </row>
+    <row r="275" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="17"/>
       <c r="B275" s="18"/>
       <c r="C275" s="34"/>
@@ -11740,12 +11357,11 @@
       <c r="U275" s="18"/>
       <c r="V275" s="18"/>
       <c r="W275" s="18"/>
-      <c r="X275" s="18"/>
-      <c r="Y275" s="25"/>
-      <c r="Z275" s="28"/>
-      <c r="AA275" s="23"/>
-    </row>
-    <row r="276" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X275" s="25"/>
+      <c r="Y275" s="28"/>
+      <c r="Z275" s="23"/>
+    </row>
+    <row r="276" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="17"/>
       <c r="B276" s="18"/>
       <c r="C276" s="34"/>
@@ -11769,12 +11385,11 @@
       <c r="U276" s="18"/>
       <c r="V276" s="18"/>
       <c r="W276" s="18"/>
-      <c r="X276" s="18"/>
-      <c r="Y276" s="25"/>
-      <c r="Z276" s="28"/>
-      <c r="AA276" s="23"/>
-    </row>
-    <row r="277" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X276" s="25"/>
+      <c r="Y276" s="28"/>
+      <c r="Z276" s="23"/>
+    </row>
+    <row r="277" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="17"/>
       <c r="B277" s="18"/>
       <c r="C277" s="34"/>
@@ -11798,12 +11413,11 @@
       <c r="U277" s="18"/>
       <c r="V277" s="18"/>
       <c r="W277" s="18"/>
-      <c r="X277" s="18"/>
-      <c r="Y277" s="25"/>
-      <c r="Z277" s="28"/>
-      <c r="AA277" s="23"/>
-    </row>
-    <row r="278" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X277" s="25"/>
+      <c r="Y277" s="28"/>
+      <c r="Z277" s="23"/>
+    </row>
+    <row r="278" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="17"/>
       <c r="B278" s="18"/>
       <c r="C278" s="34"/>
@@ -11827,12 +11441,11 @@
       <c r="U278" s="18"/>
       <c r="V278" s="18"/>
       <c r="W278" s="18"/>
-      <c r="X278" s="18"/>
-      <c r="Y278" s="25"/>
-      <c r="Z278" s="28"/>
-      <c r="AA278" s="23"/>
-    </row>
-    <row r="279" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X278" s="25"/>
+      <c r="Y278" s="28"/>
+      <c r="Z278" s="23"/>
+    </row>
+    <row r="279" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="17"/>
       <c r="B279" s="18"/>
       <c r="C279" s="34"/>
@@ -11856,12 +11469,11 @@
       <c r="U279" s="18"/>
       <c r="V279" s="18"/>
       <c r="W279" s="18"/>
-      <c r="X279" s="18"/>
-      <c r="Y279" s="25"/>
-      <c r="Z279" s="28"/>
-      <c r="AA279" s="23"/>
-    </row>
-    <row r="280" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X279" s="25"/>
+      <c r="Y279" s="28"/>
+      <c r="Z279" s="23"/>
+    </row>
+    <row r="280" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="17"/>
       <c r="B280" s="18"/>
       <c r="C280" s="34"/>
@@ -11885,12 +11497,11 @@
       <c r="U280" s="18"/>
       <c r="V280" s="18"/>
       <c r="W280" s="18"/>
-      <c r="X280" s="18"/>
-      <c r="Y280" s="25"/>
-      <c r="Z280" s="28"/>
-      <c r="AA280" s="23"/>
-    </row>
-    <row r="281" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X280" s="25"/>
+      <c r="Y280" s="28"/>
+      <c r="Z280" s="23"/>
+    </row>
+    <row r="281" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="17"/>
       <c r="B281" s="18"/>
       <c r="C281" s="34"/>
@@ -11914,12 +11525,11 @@
       <c r="U281" s="18"/>
       <c r="V281" s="18"/>
       <c r="W281" s="18"/>
-      <c r="X281" s="18"/>
-      <c r="Y281" s="25"/>
-      <c r="Z281" s="28"/>
-      <c r="AA281" s="23"/>
-    </row>
-    <row r="282" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X281" s="25"/>
+      <c r="Y281" s="28"/>
+      <c r="Z281" s="23"/>
+    </row>
+    <row r="282" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="17"/>
       <c r="B282" s="18"/>
       <c r="C282" s="34"/>
@@ -11943,12 +11553,11 @@
       <c r="U282" s="18"/>
       <c r="V282" s="18"/>
       <c r="W282" s="18"/>
-      <c r="X282" s="18"/>
-      <c r="Y282" s="25"/>
-      <c r="Z282" s="28"/>
-      <c r="AA282" s="23"/>
-    </row>
-    <row r="283" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X282" s="25"/>
+      <c r="Y282" s="28"/>
+      <c r="Z282" s="23"/>
+    </row>
+    <row r="283" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="17"/>
       <c r="B283" s="18"/>
       <c r="C283" s="34"/>
@@ -11972,12 +11581,11 @@
       <c r="U283" s="18"/>
       <c r="V283" s="18"/>
       <c r="W283" s="18"/>
-      <c r="X283" s="18"/>
-      <c r="Y283" s="25"/>
-      <c r="Z283" s="28"/>
-      <c r="AA283" s="23"/>
-    </row>
-    <row r="284" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X283" s="25"/>
+      <c r="Y283" s="28"/>
+      <c r="Z283" s="23"/>
+    </row>
+    <row r="284" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="17"/>
       <c r="B284" s="18"/>
       <c r="C284" s="34"/>
@@ -12001,12 +11609,11 @@
       <c r="U284" s="18"/>
       <c r="V284" s="18"/>
       <c r="W284" s="18"/>
-      <c r="X284" s="18"/>
-      <c r="Y284" s="25"/>
-      <c r="Z284" s="28"/>
-      <c r="AA284" s="23"/>
-    </row>
-    <row r="285" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X284" s="25"/>
+      <c r="Y284" s="28"/>
+      <c r="Z284" s="23"/>
+    </row>
+    <row r="285" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="17"/>
       <c r="B285" s="18"/>
       <c r="C285" s="34"/>
@@ -12030,12 +11637,11 @@
       <c r="U285" s="18"/>
       <c r="V285" s="18"/>
       <c r="W285" s="18"/>
-      <c r="X285" s="18"/>
-      <c r="Y285" s="25"/>
-      <c r="Z285" s="28"/>
-      <c r="AA285" s="23"/>
-    </row>
-    <row r="286" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X285" s="25"/>
+      <c r="Y285" s="28"/>
+      <c r="Z285" s="23"/>
+    </row>
+    <row r="286" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="17"/>
       <c r="B286" s="18"/>
       <c r="C286" s="34"/>
@@ -12059,12 +11665,11 @@
       <c r="U286" s="18"/>
       <c r="V286" s="18"/>
       <c r="W286" s="18"/>
-      <c r="X286" s="18"/>
-      <c r="Y286" s="25"/>
-      <c r="Z286" s="28"/>
-      <c r="AA286" s="23"/>
-    </row>
-    <row r="287" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X286" s="25"/>
+      <c r="Y286" s="28"/>
+      <c r="Z286" s="23"/>
+    </row>
+    <row r="287" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="17"/>
       <c r="B287" s="18"/>
       <c r="C287" s="34"/>
@@ -12088,12 +11693,11 @@
       <c r="U287" s="18"/>
       <c r="V287" s="18"/>
       <c r="W287" s="18"/>
-      <c r="X287" s="18"/>
-      <c r="Y287" s="25"/>
-      <c r="Z287" s="28"/>
-      <c r="AA287" s="23"/>
-    </row>
-    <row r="288" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X287" s="25"/>
+      <c r="Y287" s="28"/>
+      <c r="Z287" s="23"/>
+    </row>
+    <row r="288" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="17"/>
       <c r="B288" s="18"/>
       <c r="C288" s="34"/>
@@ -12117,12 +11721,11 @@
       <c r="U288" s="18"/>
       <c r="V288" s="18"/>
       <c r="W288" s="18"/>
-      <c r="X288" s="18"/>
-      <c r="Y288" s="25"/>
-      <c r="Z288" s="28"/>
-      <c r="AA288" s="23"/>
-    </row>
-    <row r="289" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X288" s="25"/>
+      <c r="Y288" s="28"/>
+      <c r="Z288" s="23"/>
+    </row>
+    <row r="289" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="17"/>
       <c r="B289" s="18"/>
       <c r="C289" s="34"/>
@@ -12146,12 +11749,11 @@
       <c r="U289" s="18"/>
       <c r="V289" s="18"/>
       <c r="W289" s="18"/>
-      <c r="X289" s="18"/>
-      <c r="Y289" s="25"/>
-      <c r="Z289" s="28"/>
-      <c r="AA289" s="23"/>
-    </row>
-    <row r="290" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X289" s="25"/>
+      <c r="Y289" s="28"/>
+      <c r="Z289" s="23"/>
+    </row>
+    <row r="290" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="17"/>
       <c r="B290" s="18"/>
       <c r="C290" s="34"/>
@@ -12175,12 +11777,11 @@
       <c r="U290" s="18"/>
       <c r="V290" s="18"/>
       <c r="W290" s="18"/>
-      <c r="X290" s="18"/>
-      <c r="Y290" s="25"/>
-      <c r="Z290" s="28"/>
-      <c r="AA290" s="23"/>
-    </row>
-    <row r="291" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X290" s="25"/>
+      <c r="Y290" s="28"/>
+      <c r="Z290" s="23"/>
+    </row>
+    <row r="291" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="17"/>
       <c r="B291" s="18"/>
       <c r="C291" s="34"/>
@@ -12204,12 +11805,11 @@
       <c r="U291" s="18"/>
       <c r="V291" s="18"/>
       <c r="W291" s="18"/>
-      <c r="X291" s="18"/>
-      <c r="Y291" s="25"/>
-      <c r="Z291" s="28"/>
-      <c r="AA291" s="23"/>
-    </row>
-    <row r="292" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X291" s="25"/>
+      <c r="Y291" s="28"/>
+      <c r="Z291" s="23"/>
+    </row>
+    <row r="292" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="17"/>
       <c r="B292" s="18"/>
       <c r="C292" s="34"/>
@@ -12233,12 +11833,11 @@
       <c r="U292" s="18"/>
       <c r="V292" s="18"/>
       <c r="W292" s="18"/>
-      <c r="X292" s="18"/>
-      <c r="Y292" s="25"/>
-      <c r="Z292" s="28"/>
-      <c r="AA292" s="23"/>
-    </row>
-    <row r="293" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X292" s="25"/>
+      <c r="Y292" s="28"/>
+      <c r="Z292" s="23"/>
+    </row>
+    <row r="293" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="17"/>
       <c r="B293" s="18"/>
       <c r="C293" s="34"/>
@@ -12262,12 +11861,11 @@
       <c r="U293" s="18"/>
       <c r="V293" s="18"/>
       <c r="W293" s="18"/>
-      <c r="X293" s="18"/>
-      <c r="Y293" s="25"/>
-      <c r="Z293" s="28"/>
-      <c r="AA293" s="23"/>
-    </row>
-    <row r="294" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X293" s="25"/>
+      <c r="Y293" s="28"/>
+      <c r="Z293" s="23"/>
+    </row>
+    <row r="294" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="17"/>
       <c r="B294" s="18"/>
       <c r="C294" s="34"/>
@@ -12291,12 +11889,11 @@
       <c r="U294" s="18"/>
       <c r="V294" s="18"/>
       <c r="W294" s="18"/>
-      <c r="X294" s="18"/>
-      <c r="Y294" s="25"/>
-      <c r="Z294" s="28"/>
-      <c r="AA294" s="23"/>
-    </row>
-    <row r="295" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X294" s="25"/>
+      <c r="Y294" s="28"/>
+      <c r="Z294" s="23"/>
+    </row>
+    <row r="295" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="17"/>
       <c r="B295" s="18"/>
       <c r="C295" s="34"/>
@@ -12320,12 +11917,11 @@
       <c r="U295" s="18"/>
       <c r="V295" s="18"/>
       <c r="W295" s="18"/>
-      <c r="X295" s="18"/>
-      <c r="Y295" s="25"/>
-      <c r="Z295" s="28"/>
-      <c r="AA295" s="23"/>
-    </row>
-    <row r="296" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X295" s="25"/>
+      <c r="Y295" s="28"/>
+      <c r="Z295" s="23"/>
+    </row>
+    <row r="296" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="17"/>
       <c r="B296" s="18"/>
       <c r="C296" s="34"/>
@@ -12349,12 +11945,11 @@
       <c r="U296" s="18"/>
       <c r="V296" s="18"/>
       <c r="W296" s="18"/>
-      <c r="X296" s="18"/>
-      <c r="Y296" s="25"/>
-      <c r="Z296" s="28"/>
-      <c r="AA296" s="23"/>
-    </row>
-    <row r="297" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X296" s="25"/>
+      <c r="Y296" s="28"/>
+      <c r="Z296" s="23"/>
+    </row>
+    <row r="297" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="17"/>
       <c r="B297" s="18"/>
       <c r="C297" s="34"/>
@@ -12378,12 +11973,11 @@
       <c r="U297" s="18"/>
       <c r="V297" s="18"/>
       <c r="W297" s="18"/>
-      <c r="X297" s="18"/>
-      <c r="Y297" s="25"/>
-      <c r="Z297" s="28"/>
-      <c r="AA297" s="23"/>
-    </row>
-    <row r="298" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X297" s="25"/>
+      <c r="Y297" s="28"/>
+      <c r="Z297" s="23"/>
+    </row>
+    <row r="298" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="17"/>
       <c r="B298" s="18"/>
       <c r="C298" s="34"/>
@@ -12407,12 +12001,11 @@
       <c r="U298" s="18"/>
       <c r="V298" s="18"/>
       <c r="W298" s="18"/>
-      <c r="X298" s="18"/>
-      <c r="Y298" s="25"/>
-      <c r="Z298" s="28"/>
-      <c r="AA298" s="23"/>
-    </row>
-    <row r="299" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X298" s="25"/>
+      <c r="Y298" s="28"/>
+      <c r="Z298" s="23"/>
+    </row>
+    <row r="299" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="17"/>
       <c r="B299" s="18"/>
       <c r="C299" s="34"/>
@@ -12436,12 +12029,11 @@
       <c r="U299" s="18"/>
       <c r="V299" s="18"/>
       <c r="W299" s="18"/>
-      <c r="X299" s="18"/>
-      <c r="Y299" s="25"/>
-      <c r="Z299" s="28"/>
-      <c r="AA299" s="23"/>
-    </row>
-    <row r="300" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X299" s="25"/>
+      <c r="Y299" s="28"/>
+      <c r="Z299" s="23"/>
+    </row>
+    <row r="300" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="17"/>
       <c r="B300" s="18"/>
       <c r="C300" s="34"/>
@@ -12465,12 +12057,11 @@
       <c r="U300" s="18"/>
       <c r="V300" s="18"/>
       <c r="W300" s="18"/>
-      <c r="X300" s="18"/>
-      <c r="Y300" s="25"/>
-      <c r="Z300" s="28"/>
-      <c r="AA300" s="23"/>
-    </row>
-    <row r="301" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X300" s="25"/>
+      <c r="Y300" s="28"/>
+      <c r="Z300" s="23"/>
+    </row>
+    <row r="301" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="17"/>
       <c r="B301" s="18"/>
       <c r="C301" s="34"/>
@@ -12494,12 +12085,11 @@
       <c r="U301" s="18"/>
       <c r="V301" s="18"/>
       <c r="W301" s="18"/>
-      <c r="X301" s="18"/>
-      <c r="Y301" s="25"/>
-      <c r="Z301" s="28"/>
-      <c r="AA301" s="23"/>
-    </row>
-    <row r="302" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X301" s="25"/>
+      <c r="Y301" s="28"/>
+      <c r="Z301" s="23"/>
+    </row>
+    <row r="302" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="17"/>
       <c r="B302" s="18"/>
       <c r="C302" s="34"/>
@@ -12523,12 +12113,11 @@
       <c r="U302" s="18"/>
       <c r="V302" s="18"/>
       <c r="W302" s="18"/>
-      <c r="X302" s="18"/>
-      <c r="Y302" s="25"/>
-      <c r="Z302" s="28"/>
-      <c r="AA302" s="23"/>
-    </row>
-    <row r="303" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X302" s="25"/>
+      <c r="Y302" s="28"/>
+      <c r="Z302" s="23"/>
+    </row>
+    <row r="303" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="17"/>
       <c r="B303" s="18"/>
       <c r="C303" s="34"/>
@@ -12552,12 +12141,11 @@
       <c r="U303" s="18"/>
       <c r="V303" s="18"/>
       <c r="W303" s="18"/>
-      <c r="X303" s="18"/>
-      <c r="Y303" s="25"/>
-      <c r="Z303" s="28"/>
-      <c r="AA303" s="23"/>
-    </row>
-    <row r="304" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X303" s="25"/>
+      <c r="Y303" s="28"/>
+      <c r="Z303" s="23"/>
+    </row>
+    <row r="304" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="17"/>
       <c r="B304" s="18"/>
       <c r="C304" s="34"/>
@@ -12581,12 +12169,11 @@
       <c r="U304" s="18"/>
       <c r="V304" s="18"/>
       <c r="W304" s="18"/>
-      <c r="X304" s="18"/>
-      <c r="Y304" s="25"/>
-      <c r="Z304" s="28"/>
-      <c r="AA304" s="23"/>
-    </row>
-    <row r="305" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X304" s="25"/>
+      <c r="Y304" s="28"/>
+      <c r="Z304" s="23"/>
+    </row>
+    <row r="305" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="17"/>
       <c r="B305" s="18"/>
       <c r="C305" s="34"/>
@@ -12610,12 +12197,11 @@
       <c r="U305" s="18"/>
       <c r="V305" s="18"/>
       <c r="W305" s="18"/>
-      <c r="X305" s="18"/>
-      <c r="Y305" s="25"/>
-      <c r="Z305" s="28"/>
-      <c r="AA305" s="23"/>
-    </row>
-    <row r="306" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X305" s="25"/>
+      <c r="Y305" s="28"/>
+      <c r="Z305" s="23"/>
+    </row>
+    <row r="306" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="17"/>
       <c r="B306" s="18"/>
       <c r="C306" s="34"/>
@@ -12639,12 +12225,11 @@
       <c r="U306" s="18"/>
       <c r="V306" s="18"/>
       <c r="W306" s="18"/>
-      <c r="X306" s="18"/>
-      <c r="Y306" s="25"/>
-      <c r="Z306" s="28"/>
-      <c r="AA306" s="23"/>
-    </row>
-    <row r="307" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X306" s="25"/>
+      <c r="Y306" s="28"/>
+      <c r="Z306" s="23"/>
+    </row>
+    <row r="307" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="17"/>
       <c r="B307" s="18"/>
       <c r="C307" s="34"/>
@@ -12668,12 +12253,11 @@
       <c r="U307" s="18"/>
       <c r="V307" s="18"/>
       <c r="W307" s="18"/>
-      <c r="X307" s="18"/>
-      <c r="Y307" s="25"/>
-      <c r="Z307" s="28"/>
-      <c r="AA307" s="23"/>
-    </row>
-    <row r="308" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X307" s="25"/>
+      <c r="Y307" s="28"/>
+      <c r="Z307" s="23"/>
+    </row>
+    <row r="308" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="17"/>
       <c r="B308" s="18"/>
       <c r="C308" s="34"/>
@@ -12697,12 +12281,11 @@
       <c r="U308" s="18"/>
       <c r="V308" s="18"/>
       <c r="W308" s="18"/>
-      <c r="X308" s="18"/>
-      <c r="Y308" s="25"/>
-      <c r="Z308" s="28"/>
-      <c r="AA308" s="23"/>
-    </row>
-    <row r="309" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X308" s="25"/>
+      <c r="Y308" s="28"/>
+      <c r="Z308" s="23"/>
+    </row>
+    <row r="309" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="17"/>
       <c r="B309" s="18"/>
       <c r="C309" s="34"/>
@@ -12726,12 +12309,11 @@
       <c r="U309" s="18"/>
       <c r="V309" s="18"/>
       <c r="W309" s="18"/>
-      <c r="X309" s="18"/>
-      <c r="Y309" s="25"/>
-      <c r="Z309" s="28"/>
-      <c r="AA309" s="23"/>
-    </row>
-    <row r="310" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X309" s="25"/>
+      <c r="Y309" s="28"/>
+      <c r="Z309" s="23"/>
+    </row>
+    <row r="310" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="17"/>
       <c r="B310" s="18"/>
       <c r="C310" s="34"/>
@@ -12755,12 +12337,11 @@
       <c r="U310" s="18"/>
       <c r="V310" s="18"/>
       <c r="W310" s="18"/>
-      <c r="X310" s="18"/>
-      <c r="Y310" s="25"/>
-      <c r="Z310" s="28"/>
-      <c r="AA310" s="23"/>
-    </row>
-    <row r="311" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X310" s="25"/>
+      <c r="Y310" s="28"/>
+      <c r="Z310" s="23"/>
+    </row>
+    <row r="311" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="17"/>
       <c r="B311" s="18"/>
       <c r="C311" s="34"/>
@@ -12784,12 +12365,11 @@
       <c r="U311" s="18"/>
       <c r="V311" s="18"/>
       <c r="W311" s="18"/>
-      <c r="X311" s="18"/>
-      <c r="Y311" s="25"/>
-      <c r="Z311" s="28"/>
-      <c r="AA311" s="23"/>
-    </row>
-    <row r="312" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X311" s="25"/>
+      <c r="Y311" s="28"/>
+      <c r="Z311" s="23"/>
+    </row>
+    <row r="312" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="17"/>
       <c r="B312" s="18"/>
       <c r="C312" s="34"/>
@@ -12813,12 +12393,11 @@
       <c r="U312" s="18"/>
       <c r="V312" s="18"/>
       <c r="W312" s="18"/>
-      <c r="X312" s="18"/>
-      <c r="Y312" s="25"/>
-      <c r="Z312" s="28"/>
-      <c r="AA312" s="23"/>
-    </row>
-    <row r="313" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="X312" s="25"/>
+      <c r="Y312" s="28"/>
+      <c r="Z312" s="23"/>
+    </row>
+    <row r="313" spans="1:26" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="17"/>
       <c r="B313" s="18"/>
       <c r="C313" s="34"/>
@@ -12842,15 +12421,14 @@
       <c r="U313" s="18"/>
       <c r="V313" s="18"/>
       <c r="W313" s="18"/>
-      <c r="X313" s="18"/>
-      <c r="Y313" s="25"/>
-      <c r="Z313" s="28"/>
-      <c r="AA313" s="23"/>
+      <c r="X313" s="25"/>
+      <c r="Y313" s="28"/>
+      <c r="Z313" s="23"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="WSfS1lZ8kacDNyVaxFzo9JPd2T04henfR+FzIyHgDZu2rs3Z+ajnE5KXC2A05ayzCpli37ejZ/Xkvhe8nRTr6g==" saltValue="umdfBuErJewyS9GKDy8Avg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="En0vXsajpfxO5yEroo0c4dhRZu/GFQa1o1SeE6T49iqWV1FOvsR//J+d3MULVuTY5VPl21eGGm+D1XLONVcgyg==" saltValue="QZUcBNTy7uZRFOcygxad6g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
-    <protectedRange sqref="A3:AA420" name="Rango1"/>
+    <protectedRange sqref="A3:Z420" name="Rango1"/>
   </protectedRanges>
   <conditionalFormatting sqref="O3:O116">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
@@ -12909,7 +12487,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="55" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -12925,7 +12503,7 @@
       </c>
       <c r="G3" s="1"/>
       <c r="I3" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L3" s="33"/>
       <c r="M3" s="33"/>
@@ -12938,7 +12516,7 @@
         <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L4" s="33"/>
       <c r="M4" s="33"/>
@@ -12951,7 +12529,7 @@
         <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L5" s="33"/>
       <c r="M5" s="33"/>
@@ -12961,7 +12539,7 @@
         <v>24</v>
       </c>
       <c r="I6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L6" s="33"/>
       <c r="M6" s="33"/>
@@ -12971,7 +12549,7 @@
         <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L7" s="33"/>
       <c r="M7" s="33"/>
@@ -12999,7 +12577,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
@@ -13058,7 +12636,7 @@
     </row>
     <row r="19" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D19" t="s">
         <v>37</v>
@@ -13124,7 +12702,7 @@
     </row>
     <row r="28" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D28" t="s">
         <v>46</v>
@@ -13162,7 +12740,7 @@
     </row>
     <row r="33" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -13207,7 +12785,7 @@
     </row>
     <row r="39" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C39" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D39" t="s">
         <v>56</v>
@@ -13224,7 +12802,7 @@
     </row>
     <row r="41" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C41" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D41" t="s">
         <v>58</v>
@@ -13255,7 +12833,7 @@
     </row>
     <row r="45" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C45" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D45" t="s">
         <v>61</v>
@@ -13293,7 +12871,7 @@
     </row>
     <row r="50" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C50" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D50" t="s">
         <v>66</v>
@@ -13352,7 +12930,7 @@
     </row>
     <row r="58" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C58" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D58" t="s">
         <v>74</v>
@@ -13383,7 +12961,7 @@
     </row>
     <row r="62" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C62" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D62" t="s">
         <v>78</v>
@@ -13484,7 +13062,7 @@
     </row>
     <row r="76" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C76" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D76" t="s">
         <v>92</v>
@@ -13697,7 +13275,7 @@
     </row>
     <row r="106" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C106" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D106" t="s">
         <v>122</v>
@@ -13763,7 +13341,7 @@
     </row>
     <row r="115" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C115" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D115" t="s">
         <v>131</v>
@@ -13843,7 +13421,7 @@
     </row>
     <row r="126" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C126" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D126" t="s">
         <v>142</v>
@@ -13867,7 +13445,7 @@
     </row>
     <row r="129" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C129" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D129" t="s">
         <v>145</v>
@@ -14311,7 +13889,7 @@
     </row>
     <row r="192" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C192" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D192" t="s">
         <v>208</v>
@@ -14335,7 +13913,7 @@
     </row>
     <row r="195" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C195" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D195" t="s">
         <v>211</v>
